--- a/jpcore-r4b/develop/StructureDefinition-jp-plandefinition-chemotherapyregimen.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-plandefinition-chemotherapyregimen.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -9151,10 +9151,10 @@
         <v>80</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>146</v>
+        <v>78</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>78</v>

--- a/jpcore-r4b/develop/StructureDefinition-jp-plandefinition-chemotherapyregimen.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-plandefinition-chemotherapyregimen.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev</t>
+    <t>2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Name</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -361,7 +361,7 @@
     <t>IETF language tag</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -644,7 +644,7 @@
     <t>The type of PlanDefinition.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/plan-definition-type</t>
+    <t>http://hl7.org/fhir/ValueSet/plan-definition-type|4.3.0</t>
   </si>
   <si>
     <t>PlanDefinition.status</t>
@@ -703,7 +703,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Group)canonical(MedicinalProductDefinition|SubstanceDefinition|AdministrableProductDefinition|ManufacturedItemDefinition|PackagedProductDefinition)</t>
+Reference(Group|4.3.0)canonical(MedicinalProductDefinition|4.3.0|SubstanceDefinition|4.3.0|AdministrableProductDefinition|4.3.0|ManufacturedItemDefinition|4.3.0|PackagedProductDefinition|4.3.0)</t>
   </si>
   <si>
     <t>Type of individual the plan definition is focused on</t>
@@ -721,7 +721,7 @@
     <t>The possible types of subjects for a plan definition (E.g. Patient, Practitioner, Organization, Location, etc.).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/subject-type</t>
+    <t>http://hl7.org/fhir/ValueSet/subject-type|4.3.0</t>
   </si>
   <si>
     <t>Definition.subject</t>
@@ -861,7 +861,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.3.0</t>
   </si>
   <si>
     <t>Definition.jurisdiction</t>
@@ -999,7 +999,7 @@
     <t>High-level categorization of the definition, used for searching, sorting, and filtering.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/definition-topic</t>
+    <t>http://hl7.org/fhir/ValueSet/definition-topic|4.3.0</t>
   </si>
   <si>
     <t>Definition.subject[x]</t>
@@ -1072,7 +1072,7 @@
     <t>PlanDefinition.library</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(Library)
+    <t xml:space="preserve">canonical(Library|4.3.0)
 </t>
   </si>
   <si>
@@ -1158,7 +1158,7 @@
     <t>Example codes for grouping goals for filtering or presentation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/goal-category</t>
+    <t>http://hl7.org/fhir/ValueSet/goal-category|4.3.0</t>
   </si>
   <si>
     <t>PlanDefinition.goal.description</t>
@@ -1176,7 +1176,7 @@
     <t>Describes goals that can be achieved.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.3.0</t>
   </si>
   <si>
     <t>PlanDefinition.goal.priority</t>
@@ -1191,7 +1191,7 @@
     <t>Indicates the level of importance associated with reaching or sustaining a goal.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/goal-priority</t>
+    <t>http://hl7.org/fhir/ValueSet/goal-priority|4.3.0</t>
   </si>
   <si>
     <t>PlanDefinition.goal.start</t>
@@ -1206,7 +1206,7 @@
     <t>Identifies the types of events that might trigger the start of a goal.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/goal-start-event</t>
+    <t>http://hl7.org/fhir/ValueSet/goal-start-event|4.3.0</t>
   </si>
   <si>
     <t>PlanDefinition.goal.addresses</t>
@@ -1221,7 +1221,7 @@
     <t>Identifies problems, conditions, issues, or concerns that goals may address.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.3.0</t>
   </si>
   <si>
     <t>PlanDefinition.goal.documentation</t>
@@ -1263,7 +1263,7 @@
     <t>Identifies types of parameters that can be tracked to determine goal achievement.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.3.0</t>
   </si>
   <si>
     <t>PlanDefinition.goal.target.detail[x]</t>
@@ -1322,7 +1322,7 @@
     <t>timingDaysOfCycle</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {timing-daysOfCycle}
+    <t xml:space="preserve">Extension {timing-daysOfCycle|5.2.0}
 </t>
   </si>
   <si>
@@ -1404,7 +1404,7 @@
     <t>Provides examples of actions to be performed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/action-code</t>
+    <t>http://hl7.org/fhir/ValueSet/action-code|4.3.0</t>
   </si>
   <si>
     <t>.classCode</t>
@@ -1425,7 +1425,7 @@
     <t>Provides examples of reasons for actions to be performed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/action-reason-code</t>
+    <t>http://hl7.org/fhir/ValueSet/action-reason-code|4.3.0</t>
   </si>
   <si>
     <t>.reasonCode</t>
@@ -1453,7 +1453,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Group)canonical</t>
+Reference(Group|4.3.0)canonical</t>
   </si>
   <si>
     <t>Type of individual the action is focused on</t>
@@ -1714,7 +1714,7 @@
     <t>The type of action to be performed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/action-type</t>
+    <t>http://hl7.org/fhir/ValueSet/action-type|4.3.0</t>
   </si>
   <si>
     <t>.moodCode { Maybe? this is effectively Create, Update, or Delete }</t>
@@ -1817,7 +1817,7 @@
     <t>PlanDefinition.action.transform</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureMap)
+    <t xml:space="preserve">canonical(StructureMap|4.3.0)
 </t>
   </si>
   <si>
@@ -2188,17 +2188,17 @@
   <dimension ref="A1:AN110"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.84375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="50.84375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="18.56640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="43.58984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="43.58984375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="15.91796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="186.5859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="159.96484375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2207,26 +2207,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.65625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.19140625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="44.328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.17578125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="38.00390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="39.70703125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="133.84765625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="48.05859375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="34.04296875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="114.75" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="41.19921875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4b/develop/StructureDefinition-jp-plandefinition-chemotherapyregimen.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-plandefinition-chemotherapyregimen.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-plandefinition-chemotherapyregimen.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-plandefinition-chemotherapyregimen.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3970" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3970" uniqueCount="603">
   <si>
     <t>Property</t>
   </si>
@@ -265,8 +265,8 @@
     <t>TBD</t>
   </si>
   <si>
-    <t>cnl-0:Name should be usable as an identifier for the module by machine processing applications such as code generation {name.exists() implies name.matches('[A-Z]([A-Za-z0-9_]){0,254}')}
-dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+    <t>cnl-0:名称は、コード生成などの機械処理アプリケーションによるモジュールの識別子として使用できるべきである / Name should be usable as an identifier for the module by machine processing applications such as code generation {name.exists() implies name.matches('[A-Z]([A-Za-z0-9_]){0,254}')}
+dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Act[classCode=GROUPER;moodCode=DEFN]</t>
@@ -288,13 +288,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>リソースのURLで使用されるリソースの論理ID。割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、IDが作成操作を使用してサーバーに送信されている場合です。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -307,16 +307,16 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -327,13 +327,13 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールのセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソースが構築されたときに従った一連のルールへの参照。コンテンツの処理時に理解する必要があります。多くの場合、これは他のプロファイルなどとともに特別なルールを定義する実装ガイドへの参照です。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することは、コンテンツが限られた取引パートナーのセットによってのみ理解されることを制限します。これにより、本質的に長期的にデータの有用性が制限されます。ただし、既存の健康エコシステムは非常に破壊されており、一般的に計算可能な意味でデータを定義、収集、交換する準備ができていません。可能な限り、実装者や仕様ライターはこの要素の使用を避ける必要があります。多くの場合、使用する場合、URLは、これらの特別なルールを他のプロファイル、バリューセットなどとともに叙述(Narative)の一部として定義する実装ガイドへの参照です。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -346,19 +346,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語は、インデックス作成とアクセシビリティをサポートするために提供されます（通常、テキストから音声までのサービスなどのサービスが言語タグを使用します）。叙述(Narative)のHTML言語タグは、叙述(Narative)に適用されます。リソース上の言語タグを使用して、リソース内のデータから生成された他のプレゼンテーションの言語を指定できます。すべてのコンテンツが基本言語である必要はありません。リソース。言語は、叙述(Narative)に自動的に適用されると想定されるべきではありません。言語が指定されている場合、HTMLのDIV要素にも指定されている場合（XML：LangとHTML Lang属性の関係については、HTML5のルールを参照してください）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>IETF言語タグ / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -378,13 +378,13 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>人間の解釈のためのリソースのテキスト概要 / Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>リソースの概要を含み、人間へのリソースの内容を表すために使用できる人間の読み取り可能な叙述(Narative)。叙述(Narative)はすべての構造化されたデータをエンコードする必要はありませんが、人間が叙述(Narative)を読むだけで「臨床的に安全」にするために十分な詳細を含める必要があります。リソースの定義は、臨床的安全を確保するために、叙述(Narative)で表現するコンテンツを定義する場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには叙述(Narative)がありません。含まれていないリソースには叙述(Narative)が必要です。場合によっては、リソースには、追加の個別のデータがほとんどまたはまったくないテキストのみがあります（すべてのMinoccur = 1要素が満たされている限り）。これは、情報がtext blob (バイナリー ラージ オブジェクト)としてキャプチャされるレガシーシステムからのデータ、またはテキストが生またはナレーションされ、エンコードされた情報が後で追加される場合に必要になる場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -404,19 +404,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>インラインリソースが含まれています / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースには、それらを含むリソースを除いて独立した存在はありません - 独立して特定することはできず、独自の独立したトランザクションスコープを持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>識別が失われると、コンテンツを適切に識別できる場合は、これを行うべきではありません。含まれるリソースには、メタ要素にプロファイルとタグがある場合がありますが、セキュリティラベルはありません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -446,944 +446,952 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>PlanDefinition.extension:regimenType</t>
+  </si>
+  <si>
+    <t>regimenType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_PlanDefinition_ChemotherapyRegimen_RegimenType}
+</t>
+  </si>
+  <si>
+    <t>【仮】レジメン種別に関する情報</t>
+  </si>
+  <si>
+    <t>レジメン種別に関する情報を格納するためのExtension。</t>
+  </si>
+  <si>
+    <t>レジメン種別に関する情報を表現する拡張</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>PlanDefinition.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではなく、それを含む要素の理解および/または含有要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>PlanDefinition.url</t>
+  </si>
+  <si>
+    <t>この計画定義の標準identifier、URI（グローバルにユニーク）として表される / Canonical identifier for this plan definition, represented as a URI (globally unique)</t>
+  </si>
+  <si>
+    <t>この計画定義を特定するために使用される絶対URIは、仕様、モデル、設計、またはインスタンスで参照されている場合に使用されます。その標準identifierとも呼ばれます。これはグローバルにユニークである必要があり、この計画定義の権威あるインスタンスが公開される（または公開される）文字通りのアドレスである必要があります。このURLは、標準的な参照のターゲットになる可能性があります。計画定義が異なるサーバーに保存されている場合、同じままになります。 / An absolute URI that is used to identify this plan definition when it is referenced in a specification, model, design or an instance; also called its canonical identifier. This SHOULD be globally unique and SHOULD be a literal address at which at which an authoritative instance of this plan definition is (or will be) published. This URL can be the target of a canonical reference. It SHALL remain the same when the plan definition is stored on different servers.</t>
+  </si>
+  <si>
+    <t>urn：uuid：またはurn：oid：しかし、実際のhttp：アドレスが望ましいです。複数のインスタンスが異なるバージョンがある場合、同じURLを共有する場合があります。
+新しいバージョンのリソース（同じURL、新しいバージョン）を作成するタイミングの決定と新しいアーティファクトの定義は、著者次第です。この決定を行うための考慮事項は、[テクニカルバージョンとビジネスバージョン]（resource.html＃バージョン）にあります。
+場合によっては、リソースは記載されているURLで見つけることができなくなりますが、URL自体は変更できません。実装では、[Meta.Source]（Resource.html＃Meta）要素を使用して、リソースの現在のマスターソースがどこにあるかを示すことができます。 / Can be a urn:uuid: or a urn:oid: but real http: addresses are preferred.  Multiple instances may share the same URL if they have a distinct version.
+The determination of when to create a new version of a resource (same url, new version) vs. defining a new artifact is up to the author.  Considerations for making this decision are found in [Technical and Business Versions](http://hl7.org/fhir/R4B/resource.html#versions). 
+In some cases, the resource can no longer be found at the stated url, but the url itself cannot change. Implementations can use the [meta.source](http://hl7.org/fhir/R4B/resource.html#meta) element to indicate where the current master source of the resource can be found.</t>
+  </si>
+  <si>
+    <t>プラン定義を、単一のグローバルに一意のidentifierによって参照できるようにします。 / Allows the plan definition to be referenced by a single globally unique identifier.</t>
+  </si>
+  <si>
+    <t>Definition.url</t>
+  </si>
+  <si>
+    <t>.identifier[scope=BUSN;reliability=ISS]</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>PlanDefinition.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>計画定義の追加identifier / Additional identifier for the plan definition</t>
+  </si>
+  <si>
+    <t>他の形式で表されている場合、または仕様、モデル、設計、またはインスタンスで参照される場合に、この計画定義を識別するために使用される正式なidentifier。 / A formal identifier that is used to identify this plan definition when it is represented in other formats, or referenced in a specification, model, design or an instance.</t>
+  </si>
+  <si>
+    <t>通常、これは、HL7 V3 II（インスタンスidentifier）データ型に移動できるidentifierに使用され、論理URIを使用できないFHIR以外でこの計画定義を識別できます。 / Typically, this is used for identifiers that can go in an HL7 V3 II (instance identifier) data type, and can then identify this plan definition outside of FHIR, where it is not possible to use the logical URI.</t>
+  </si>
+  <si>
+    <t>外部から提供可能なビジネスidentifierをモジュールに簡単に関連付けることができます。 / Allows externally provided and/or usable business identifiers to be easily associated with the module.</t>
+  </si>
+  <si>
+    <t>Definition.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>no-gen-base</t>
+  </si>
+  <si>
+    <t>PlanDefinition.version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>計画定義のビジネスバージョン / Business version of the plan definition</t>
+  </si>
+  <si>
+    <t>プラン定義のこのバージョンを識別するために使用されるidentifierは、仕様、モデル、設計、またはインスタンスで参照されている場合に使用されます。これは、計画定義著者によって管理される任意の価値であり、グローバルにユニークであるとは期待されていません。たとえば、マネージドバージョンが利用できない場合は、タイムスタンプ（Yyyymmddなど）かもしれません。また、バージョンを辞書的なシーケンスに配置できるという期待もありません。意思決定サポートサービスの仕様と一致するバージョンを提供するには、Major.minor.revisionの形式（1.0.0など）を使用します。バージョンの知識資産の詳細については、意思決定支援サービスの仕様を参照してください。非実験的アクティブアーティファクトにはバージョンが必要であることに注意してください。 / The identifier that is used to identify this version of the plan definition when it is referenced in a specification, model, design or instance. This is an arbitrary value managed by the plan definition author and is not expected to be globally unique. For example, it might be a timestamp (e.g. yyyymmdd) if a managed version is not available. There is also no expectation that versions can be placed in a lexicographical sequence. To provide a version consistent with the Decision Support Service specification, use the format Major.Minor.Revision (e.g. 1.0.0). For more information on versioning knowledge assets, refer to the Decision Support Service specification. Note that a version is required for non-experimental active artifacts.</t>
+  </si>
+  <si>
+    <t>同じidentifierを持っているが異なるバージョンを持つさまざまなプラン定義インスタンスがある場合があります。バージョンは、[url] | [バージョン]を使用して、プラン定義の特定のビジネスバージョンへの参照を許可するために、参照でURLに追加できます。 / There may be different plan definition instances that have the same identifier but different versions.  The version can be appended to the url in a reference to allow a reference to a particular business version of the plan definition with the format [url]|[version].</t>
+  </si>
+  <si>
+    <t>Definition.version</t>
+  </si>
+  <si>
+    <t>N/A (to add?)</t>
+  </si>
+  <si>
+    <t>FiveWs.version</t>
+  </si>
+  <si>
+    <t>PlanDefinition.name</t>
+  </si>
+  <si>
+    <t>この計画の定義の名前（コンピューターフレンドリー） / Name for this plan definition (computer friendly)</t>
+  </si>
+  <si>
+    <t>計画定義を識別する自然言語名。この名前は、コード生成などのマシン処理アプリケーションにより、モジュールのidentifierとして使用できる必要があります。 / A natural language name identifying the plan definition. This name should be usable as an identifier for the module by machine processing applications such as code generation.</t>
+  </si>
+  <si>
+    <t>名前はグローバルにユニークであるとは予想されていません。名前は、機械加工に優しいことを確認するための単純な英数字タイプの名前である必要があります。 / The name is not expected to be globally unique. The name should be a simple alphanumeric type name to ensure that it is machine-processing friendly.</t>
+  </si>
+  <si>
+    <t>ヒューマンナビゲーションとコード生成をサポートします。 / Support human navigation and code generation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cnl-0
+</t>
+  </si>
+  <si>
+    <t>PlanDefinition.title</t>
+  </si>
+  <si>
+    <t>この計画の定義の名前（人間に優しい） / Name for this plan definition (human friendly)</t>
+  </si>
+  <si>
+    <t>プラン定義の短い、説明的なユーザーフレンドリーなタイトル。 / A short, descriptive, user-friendly title for the plan definition.</t>
+  </si>
+  <si>
+    <t>この名前は、機械加工に優しいものである必要はなく、句読点、ホワイトスペースなどが含まれている場合があります。 / This name does not need to be machine-processing friendly and may contain punctuation, white-space, etc.</t>
+  </si>
+  <si>
+    <t>Definition.title</t>
+  </si>
+  <si>
+    <t>.title</t>
+  </si>
+  <si>
+    <t>PlanDefinition.subtitle</t>
+  </si>
+  <si>
+    <t>計画定義の下位タイトル / Subordinate title of the plan definition</t>
+  </si>
+  <si>
+    <t>計画定義の説明または代替タイトルは、そのコンテンツに関する追加情報を提供します。 / An explanatory or alternate title for the plan definition giving additional information about its content.</t>
+  </si>
+  <si>
+    <t>PlanDefinition.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>注文セット|臨床プロトコル|ECAルール|ワークフロー定義 / order-set | clinical-protocol | eca-rule | workflow-definition</t>
+  </si>
+  <si>
+    <t>プラン定義に関心のある種類のシステムを区別する計画定義の高レベルのカテゴリ。 / A high-level category for the plan definition that distinguishes the kinds of systems that would be interested in the plan definition.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>プランディングのタイプ。 / The type of PlanDefinition.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/plan-definition-type|4.3.0</t>
+  </si>
+  <si>
+    <t>PlanDefinition.status</t>
+  </si>
+  <si>
+    <t>ドラフト|アクティブ|引退|わからない / draft | active | retired | unknown</t>
+  </si>
+  <si>
+    <t>この計画定義のステータス。コンテンツのライフサイクルを追跡することができます。 / The status of this plan definition. Enables tracking the life-cycle of the content.</t>
+  </si>
+  <si>
+    <t>使用に適した計画定義のフィルタリングを使用できます。 / Allows filtering of plan definitions that are appropriate for use versus not.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>アーティファクトのライフサイクルステータス。 / The lifecycle status of an artifact.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/publication-status|4.3.0</t>
+  </si>
+  <si>
+    <t>Definition.status {different ValueSet}</t>
+  </si>
+  <si>
+    <t>.status</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>PlanDefinition.experimental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>テスト目的で、実際の使用法ではありません / For testing purposes, not real usage</t>
+  </si>
+  <si>
+    <t>この計画の定義は、テスト目的（または教育/評価/マーケティング）のために執筆されており、真の使用に使用されることを意図していないことを示すブール値。 / A Boolean value to indicate that this plan definition is authored for testing purposes (or education/evaluation/marketing) and is not intended to be used for genuine usage.</t>
+  </si>
+  <si>
+    <t>生産レベルの計画定義に使用される同じライフサイクルに従って、実験的なコンテンツを開発できるようにします。 / Enables experimental content to be developed following the same lifecycle that would be used for a production-level plan definition.</t>
+  </si>
+  <si>
+    <t>Definition.experimental</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>PlanDefinition.subject[x]</t>
+  </si>
+  <si>
+    <t>CodeableConcept
+Reference(Group|4.3.0)canonical(MedicinalProductDefinition|4.3.0|SubstanceDefinition|4.3.0|AdministrableProductDefinition|4.3.0|ManufacturedItemDefinition|4.3.0|PackagedProductDefinition|4.3.0)</t>
+  </si>
+  <si>
+    <t>個人のタイプ計画定義は焦点を当てています / Type of individual the plan definition is focused on</t>
+  </si>
+  <si>
+    <t>プラン定義の対象となる主題を記述または識別するコード、グループ定義、またはカノニカル参照。カノニカル参照は、医薬品および物質の品質仕様のプロトコル定義をサポートするために許可されており、MedicinalProductDefinition、SubstanceDefinition、AdministrableProductDefinition、ManufacturedItemDefinition、またはPackagedProductDefinitionリソースを参照できます。 / A code, group definition, or canonical reference that describes  or identifies the intended subject of the plan definition. Canonical references are allowed to support the definition of protocols for drug and substance quality specifications, and is allowed to reference a MedicinalProductDefinition, SubstanceDefinition, AdministrableProductDefinition, ManufacturedItemDefinition, or PackagedProductDefinition resource.</t>
+  </si>
+  <si>
+    <t>subject要素のcanonical型の選択肢はR4Bで医薬品品質のユースケースをサポートするために導入されたことに注意。できるだけ後方互換性を確保するため、新しいcanonical型はこれらのユースケースでのみ使用することが推奨される。 / Note that the choice of canonical for the subject element was introduced in R4B to support pharmaceutical quality use cases. To ensure as much backwards-compatibility as possible, it is recommended to only use the new canonical type with these use cases.</t>
+  </si>
+  <si>
+    <t>忍耐強い / Patient</t>
+  </si>
+  <si>
+    <t>計画定義の可能性のある被験者（患者、開業医、組織、場所など）の可能なタイプ。 / The possible types of subjects for a plan definition (E.g. Patient, Practitioner, Organization, Location, etc.).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/subject-type|4.3.0</t>
+  </si>
+  <si>
+    <t>Definition.subject</t>
+  </si>
+  <si>
+    <t>PlanDefinition.date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revision Date
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>日付は最後に変更されました / Date last changed</t>
+  </si>
+  <si>
+    <t>計画定義が公開された日付（およびオプションでの時刻）。ビジネスバージョンが変更されたときに日付が変更され、ステータスコードが変更された場合は変更する必要があります。さらに、計画定義の実質的な内容が変更されると、変更されるはずです。 / The date  (and optionally time) when the plan definition was published. The date must change when the business version changes and it must change if the status code changes. In addition, it should change when the substantive content of the plan definition changes.</t>
+  </si>
+  <si>
+    <t>リソースは計画定義の二次表現である可能性があるため、これはリソースのラスト修飾日と同じではないことに注意してください。追加の特定の日付は、拡張機能として追加されるか、リソースの過去のバージョンに関連する提案に相談することで見つけることができます。 / Note that this is not the same as the resource last-modified-date, since the resource may be a secondary representation of the plan definition. Additional specific dates may be added as extensions or be found by consulting Provenances associated with past versions of the resource.</t>
+  </si>
+  <si>
+    <t>Definition.date</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=AUT].time</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>PlanDefinition.publisher</t>
+  </si>
+  <si>
+    <t>出版社の名前（組織または個人） / Name of the publisher (organization or individual)</t>
+  </si>
+  <si>
+    <t>計画定義を公開した組織または個人の名前。 / The name of the organization or individual that published the plan definition.</t>
+  </si>
+  <si>
+    <t>通常、組織ですが、個人かもしれません。プラン定義の出版社（またはスチュワード）は、計画定義のメンテナンスと維持の主な責任者です。これは、必ずしもコンテンツを開発し、最初に執筆した個人または組織ではありません。出版社は、計画の定義に関する質問や問題の主な連絡先です。情報がコンテキストから利用可能でない限り、このアイテムは入力する必要があります。 / Usually an organization but may be an individual. The publisher (or steward) of the plan definition is the organization or individual primarily responsible for the maintenance and upkeep of the plan definition. This is not necessarily the same individual or organization that developed and initially authored the content. The publisher is the primary point of contact for questions or issues with the plan definition. This item SHOULD be populated unless the information is available from context.</t>
+  </si>
+  <si>
+    <t>計画定義の「権限/信頼性」を確立するのに役立ちます。また、接触を許可する場合があります。 / Helps establish the "authority/credibility" of the plan definition.  May also allow for contact.</t>
+  </si>
+  <si>
+    <t>Definition.publisher</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=AUT].role</t>
+  </si>
+  <si>
+    <t>FiveWs.witness</t>
+  </si>
+  <si>
+    <t>PlanDefinition.contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ContactDetail
+</t>
+  </si>
+  <si>
+    <t>出版社の連絡先の詳細 / Contact details for the publisher</t>
+  </si>
+  <si>
+    <t>ユーザーがパブリッシャーを見つけて通信するのを支援する連絡先の詳細。 / Contact details to assist a user in finding and communicating with the publisher.</t>
+  </si>
+  <si>
+    <t>Webサイト、電子メールアドレス、電話番号などです。 / May be a web site, an email address, a telephone number, etc.</t>
+  </si>
+  <si>
+    <t>Definition.contact</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=CALLBCK].role</t>
+  </si>
+  <si>
+    <t>PlanDefinition.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">markdown
+</t>
+  </si>
+  <si>
+    <t>計画定義の自然言語の説明 / Natural language description of the plan definition</t>
+  </si>
+  <si>
+    <t>消費者の観点からの計画定義の無料テキスト自然言語説明。 / A free text natural language description of the plan definition from a consumer's perspective.</t>
+  </si>
+  <si>
+    <t>この説明は、計画定義が作成された理由、誤用に関するコメント、臨床使用と解釈の指示、文献の参照、紙の世界からの例などの詳細をキャプチャするために使用できます。これは、伝えられる計画定義のレンダリングではありません。リソース自体の「テキスト」フィールド。この項目は、情報がコンテキストから利用可能でない限り入力する必要があります（たとえば、計画定義の言語は、計画定義が作成された場所の主要な言語であると推定されます）。 / This description can be used to capture details such as why the plan definition was built, comments about misuse, instructions for clinical use and interpretation, literature references, examples from the paper world, etc. It is not a rendering of the plan definition as conveyed in the 'text' field of the resource itself. This item SHOULD be populated unless the information is available from context (e.g. the language of the plan definition is presumed to be the predominant language in the place the plan definition was created).</t>
+  </si>
+  <si>
+    <t>Definition.description</t>
+  </si>
+  <si>
+    <t>.text</t>
+  </si>
+  <si>
+    <t>PlanDefinition.useContext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UsageContext
+</t>
+  </si>
+  <si>
+    <t>【仮】対象疾患</t>
+  </si>
+  <si>
+    <t>コンテンツは、リストされているコンテキストをサポートすることを目的として開発されました。これらのコンテキストは、一般的なカテゴリ（性別、年齢、...）であるか、特定のプログラム（保険プラン、研究など）への参照である場合があり、適切な計画定義インスタンスのインデックス作成と検索を支援するために使用できます。 / The content was developed with a focus and intent of supporting the contexts that are listed. These contexts may be general categories (gender, age, ...) or may be references to specific programs (insurance plans, studies, ...) and may be used to assist with indexing and searching for appropriate plan definition instances.</t>
+  </si>
+  <si>
+    <t>複数のUSECONTEXTSが指定されている場合、すべてまたはどのコンテキストが適用されるという期待はありません。 / When multiple useContexts are specified, there is no expectation that all or any of the contexts apply.</t>
+  </si>
+  <si>
+    <t>適切なコンテンツの検索を支援します。 / Assist in searching for appropriate content.</t>
+  </si>
+  <si>
+    <t>Definition.useContext</t>
+  </si>
+  <si>
+    <t>PlanDefinition.jurisdiction</t>
+  </si>
+  <si>
+    <t>計画定義のための対象管轄区域（該当する場合） / Intended jurisdiction for plan definition (if applicable)</t>
+  </si>
+  <si>
+    <t>計画定義を使用することを目的としている法的または地理的地域。 / A legal or geographic region in which the plan definition is intended to be used.</t>
+  </si>
+  <si>
+    <t>計画定義は、元々設計または意図されたもの以外の管轄区域で使用される可能性があります。 / It may be possible for the plan definition to be used in jurisdictions other than those for which it was originally designed or intended.</t>
+  </si>
+  <si>
+    <t>このアーティファクトが使用することを目的としている国と地域。 / Countries and regions within which this artifact is targeted for use.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.3.0</t>
+  </si>
+  <si>
+    <t>Definition.jurisdiction</t>
+  </si>
+  <si>
+    <t>PlanDefinition.purpose</t>
+  </si>
+  <si>
+    <t>この計画定義が定義されている理由 / Why this plan definition is defined</t>
+  </si>
+  <si>
+    <t>この計画定義が必要な理由と、それがそのまま設計された理由の説明。 / Explanation of why this plan definition is needed and why it has been designed as it has.</t>
+  </si>
+  <si>
+    <t>この要素は、計画定義の使用法を説明していません。代わりに、リソースが必要であるか、「なぜ」のどちらかのように定義されている「なぜ」のトレーサビリティを提供します。これは、この計画定義の構造を促進する材料または仕様を調達するために使用できます。 / This element does not describe the usage of the plan definition. Instead, it provides traceability of ''why'' the resource is either needed or ''why'' it is defined as it is.  This may be used to point to source materials or specifications that drove the structure of this plan definition.</t>
+  </si>
+  <si>
+    <t>Definition.purpose</t>
+  </si>
+  <si>
+    <t>.reasonCode.text</t>
+  </si>
+  <si>
+    <t>FiveWs.why[x]</t>
+  </si>
+  <si>
+    <t>PlanDefinition.usage</t>
+  </si>
+  <si>
+    <t>計画の臨床的使用について説明します / Describes the clinical usage of the plan</t>
+  </si>
+  <si>
+    <t>臨床的観点から計画定義がどのように使用されるかの詳細な説明。 / A detailed description of how the plan definition is used from a clinical perspective.</t>
+  </si>
+  <si>
+    <t>PlanDefinition.copyright</t>
+  </si>
+  <si>
+    <t>License
+Restrictions</t>
+  </si>
+  <si>
+    <t>使用および/または公開制限 / Use and/or publishing restrictions</t>
+  </si>
+  <si>
+    <t>計画定義および/またはその内容に関する著作権声明。著作権声明は、一般に、計画定義の使用と公開に関する法的制限です。 / A copyright statement relating to the plan definition and/or its contents. Copyright statements are generally legal restrictions on the use and publishing of the plan definition.</t>
+  </si>
+  <si>
+    <t>消費者は、計画定義および/またはそのコンテンツの使用に関する法的制限を決定できる必要があります。 / Consumers must be able to determine any legal restrictions on the use of the plan definition and/or its content.</t>
+  </si>
+  <si>
+    <t>Definition.copyright</t>
+  </si>
+  <si>
+    <t>PlanDefinition.approvalDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date
+</t>
+  </si>
+  <si>
+    <t>計画定義が出版社によって承認されたとき / When the plan definition was approved by publisher</t>
+  </si>
+  <si>
+    <t>リソースコンテンツが出版社によって承認された日付。承認は、コンテンツの使用が正式に承認されたときに1回発生します。 / The date on which the resource content was approved by the publisher. Approval happens once when the content is officially approved for usage.</t>
+  </si>
+  <si>
+    <t>「日付」要素は、軽度の変更または編集の修正のため、承認日よりも最近のものです。 / The 'date' element may be more recent than the approval date because of minor changes or editorial corrections.</t>
+  </si>
+  <si>
+    <t>Definition.approvalDate</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="SUBJ"].act[classCode=CACT;moodCode=EVN;code="approval"].effectiveTime</t>
+  </si>
+  <si>
+    <t>PlanDefinition.lastReviewDate</t>
+  </si>
+  <si>
+    <t>計画定義が最後にレビューされたとき / When the plan definition was last reviewed</t>
+  </si>
+  <si>
+    <t>リソースコンテンツが最後にレビューされた日付。レビューは承認後に定期的に行われますが、元の承認日は変更されません。 / The date on which the resource content was last reviewed. Review happens periodically after approval but does not change the original approval date.</t>
+  </si>
+  <si>
+    <t>指定されている場合、この日付は元の承認日に従います。 / If specified, this date follows the original approval date.</t>
+  </si>
+  <si>
+    <t>コンテンツがどれほど「現在」であるかの感覚を与えます。長い間レビューされていないリソースは、適切/関連性が低くなるリスクがある場合があります。 / Gives a sense of how "current" the content is.  Resources that have not been reviewed in a long time may have a risk of being less appropriate/relevant.</t>
+  </si>
+  <si>
+    <t>Definition.lastReviewDate</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="SUBJ"; subsetCode="RECENT"].act[classCode=CACT;moodCode=EVN;code="review"].effectiveTime</t>
+  </si>
+  <si>
+    <t>PlanDefinition.effectivePeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>計画定義が使用されると予想される場合 / When the plan definition is expected to be used</t>
+  </si>
+  <si>
+    <t>プラン定義コンテンツがアクティブに使用されるか、または計画されている期間。 / The period during which the plan definition content was or is planned to be in active use.</t>
+  </si>
+  <si>
+    <t>プラン定義の有効期間は、コンテンツが使用に適用され、公開およびレビューの日付とは無関係になっている時期を決定します。たとえば、2016年に使用することを目的とした尺度は、2015年に公開される場合があります。 / The effective period for a plan definition  determines when the content is applicable for usage and is independent of publication and review dates. For example, a measure intended to be used for the year 2016 might be published in 2015.</t>
+  </si>
+  <si>
+    <t>リソースが施行される前に移行を確立することができ、計画定義の新しいバージョンが代わりに使用される場合と予想される場合、日没プロセスを許可します。 / Allows establishing a transition before a resource comes into effect and also allows for a sunsetting  process when new versions of the plan definition are or are expected to be used instead.</t>
+  </si>
+  <si>
+    <t>Definition.effectivePeriod</t>
+  </si>
+  <si>
+    <t>PlanDefinition.topic</t>
+  </si>
+  <si>
+    <t>例えば。教育、治療、評価 / E.g. Education, Treatment, Assessment</t>
+  </si>
+  <si>
+    <t>計画定義の内容に関連する説明的なトピック。トピックは、フィルタリングと検索に役立つ定義の高レベルの分類を提供します。 / Descriptive topics related to the content of the plan definition. Topics provide a high-level categorization of the definition that can be useful for filtering and searching.</t>
+  </si>
+  <si>
+    <t>リポジトリは、トピック検索によって見つけることができるように、計画定義を分類する方法を決定できる必要があります。 / Repositories must be able to determine how to categorize the plan definition so that it can be found by topical searches.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>検索、ソート、フィルタリングに使用される定義の高レベルの分類。 / High-level categorization of the definition, used for searching, sorting, and filtering.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/definition-topic|4.3.0</t>
+  </si>
+  <si>
+    <t>Definition.subject[x]</t>
+  </si>
+  <si>
+    <t>PlanDefinition.author</t>
+  </si>
+  <si>
+    <t>誰がコンテンツを執筆しましたか / Who authored the content</t>
+  </si>
+  <si>
+    <t>主にコンテンツの作成とメンテナンスに関与する個人または組織。 / An individiual or organization primarily involved in the creation and maintenance of the content.</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=AUT]</t>
+  </si>
+  <si>
+    <t>PlanDefinition.editor</t>
+  </si>
+  <si>
+    <t>コンテンツを編集した人 / Who edited the content</t>
+  </si>
+  <si>
+    <t>主にコンテンツの内部一貫性を担当する個人または組織。 / An individual or organization primarily responsible for internal coherence of the content.</t>
+  </si>
+  <si>
+    <t>PlanDefinition.reviewer</t>
+  </si>
+  <si>
+    <t>コンテンツをレビューした人 / Who reviewed the content</t>
+  </si>
+  <si>
+    <t>コンテンツのいくつかの側面のレビューを主に担当する個人または組織。 / An individual or organization primarily responsible for review of some aspect of the content.</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=VRF] {not clear whether VRF best corresponds to reviewer or endorser}</t>
+  </si>
+  <si>
+    <t>PlanDefinition.endorser</t>
+  </si>
+  <si>
+    <t>誰がコンテンツを承認しましたか / Who endorsed the content</t>
+  </si>
+  <si>
+    <t>一部の設定で使用するためにコンテンツを公式に支持する個人または組織。 / An individual or organization responsible for officially endorsing the content for use in some setting.</t>
+  </si>
+  <si>
+    <t>PlanDefinition.relatedArtifact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RelatedArtifact
+</t>
+  </si>
+  <si>
+    <t>追加のドキュメント、引用 / Additional documentation, citations</t>
+  </si>
+  <si>
+    <t>追加のドキュメント、正当化、書誌参照などの関連アーチファクト。 / Related artifacts such as additional documentation, justification, or bibliographic references.</t>
+  </si>
+  <si>
+    <t>関連する各アーティファクトは、添付ファイルまたは別のリソースへの参照のいずれかですが、両方ではありません。 / Each related artifact is either an attachment, or a reference to another resource, but not both.</t>
+  </si>
+  <si>
+    <t>計画の定義は、コンテンツの正当化と証拠を決定および理解できるように、コンテンツの消費者（および/またはコンテンツによって生成された介入または結果）の十分な情報を提供できる必要があります。 / Plan definitions must be able to provide enough information for consumers of the content (and/or interventions or results produced by the content) to be able to determine and understand the justification for and evidence in support of the content.</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=DOC,RSON,PREV, DRIV, USE, COMP] {successor would be PREV w/ inversionInd=true; No support for citation}</t>
+  </si>
+  <si>
+    <t>PlanDefinition.library</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(Library|4.3.0)
+</t>
+  </si>
+  <si>
+    <t>計画定義で使用されるロジック / Logic used by the plan definition</t>
+  </si>
+  <si>
+    <t>計画定義で使用される正式なロジックを含むライブラリリソースへの参照。 / A reference to a Library resource containing any formal logic used by the plan definition.</t>
+  </si>
+  <si>
+    <t>PlanDefinition.goal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>計画が達成しようとしていること / What the plan is trying to accomplish</t>
+  </si>
+  <si>
+    <t>ゴールは、プラン内の活動が達成しようとする期待される結果を記述します。例えば、体重減少、日常生活動作の回復、予防接種による集団免疫の獲得、プロセス改善目標の達成、品質仕様で指定されたテストの受入基準の達成などです。 / A goal describes an expected outcome that activities within the plan are intended to achieve. For example, weight loss, restoring an activity of daily living, obtaining herd immunity via immunization, meeting a process improvement objective, meeting the acceptance criteria for a test as specified by a quality specification, etc.</t>
+  </si>
+  <si>
+    <t>目標情報は、注文セット、プロトコル、およびケア計画の定義に対してキャプチャする必要があります。これは、プロトコルアクティビティの目的をよりよく説明し、派生したケア計画と注文内で特定の目標の作成を導く必要があります。 / Goal information needs to be captured for order sets, protocols, and care plan definitions to better describe the objectives of the protocol activities and to guide the creation of specific goals within the derived care plans and orders.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
+  </si>
+  <si>
+    <t>PlanDefinition.goal.id</t>
+  </si>
+  <si>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>PlanDefinition.goal.extension</t>
+  </si>
+  <si>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>PlanDefinition.goal.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>認識されていなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではなく、それが含まれている要素の理解、および/または含まれる要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>PlanDefinition.goal.category</t>
+  </si>
+  <si>
+    <t>例えば。治療、食事、行動 / E.g. Treatment, dietary, behavioral</t>
+  </si>
+  <si>
+    <t>目標が該当するカテゴリを示します。 / Indicates a category the goal falls within.</t>
+  </si>
+  <si>
+    <t>フィルタリングまたはプレゼンテーションの目標をグループ化するためのコードの例。 / Example codes for grouping goals for filtering or presentation.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/goal-category|4.3.0</t>
+  </si>
+  <si>
+    <t>PlanDefinition.goal.description</t>
+  </si>
+  <si>
+    <t>目標を説明するコードまたはテキスト / Code or text describing the goal</t>
+  </si>
+  <si>
+    <t>「コントロール血圧」や「障害物コースの交渉」、「結婚式での子供とのダンス」など、特定の希望のケアの目的の人間が読み取り可能および/またはコード化された説明。 / Human-readable and/or coded description of a specific desired objective of care, such as "control blood pressure" or "negotiate an obstacle course" or "dance with child at wedding".</t>
+  </si>
+  <si>
+    <t>コードが利用できない場合は、codeableconcept.textを使用してください。 / If no code is available, use CodeableConcept.text.</t>
+  </si>
+  <si>
+    <t>達成できる目標について説明します。 / Describes goals that can be achieved.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.3.0</t>
+  </si>
+  <si>
+    <t>PlanDefinition.goal.priority</t>
+  </si>
+  <si>
+    <t>優先度|中程度の優先度|低価格 / high-priority | medium-priority | low-priority</t>
+  </si>
+  <si>
+    <t>定義された目標に到達/維持することに関連する重要性の予想レベルを特定します。 / Identifies the expected level of importance associated with reaching/sustaining the defined goal.</t>
+  </si>
+  <si>
+    <t>目標に到達または維持することに関連する重要性のレベルを示します。 / Indicates the level of importance associated with reaching or sustaining a goal.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/goal-priority|4.3.0</t>
+  </si>
+  <si>
+    <t>PlanDefinition.goal.start</t>
+  </si>
+  <si>
+    <t>ゴール追跡が始まるとき / When goal pursuit begins</t>
+  </si>
+  <si>
+    <t>その後のイベントは、目標が追求され始めるはずです。 / The event after which the goal should begin being pursued.</t>
+  </si>
+  <si>
+    <t>ゴールの開始をトリガーする可能性のあるイベントの種類を特定します。 / Identifies the types of events that might trigger the start of a goal.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/goal-start-event|4.3.0</t>
+  </si>
+  <si>
+    <t>PlanDefinition.goal.addresses</t>
+  </si>
+  <si>
+    <t>目標は何ですか / What does the goal address</t>
+  </si>
+  <si>
+    <t>問題、条件、問題、または懸念を特定します。目標は対処することを目的としています。 / Identifies problems, conditions, issues, or concerns the goal is intended to address.</t>
+  </si>
+  <si>
+    <t>目標が対処する可能性のある問題、条件、問題、または懸念を特定します。 / Identifies problems, conditions, issues, or concerns that goals may address.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.3.0</t>
+  </si>
+  <si>
+    <t>PlanDefinition.goal.documentation</t>
+  </si>
+  <si>
+    <t>目標のドキュメントをサポートします / Supporting documentation for the goal</t>
+  </si>
+  <si>
+    <t>目標に関するさらなるサポート情報を提供する目標に関連する教訓的またはその他の情報リソース。情報リソースには、インラインテキストの解説とWebリソースへのリンクを含めることができます。 / Didactic or other informational resources associated with the goal that provide further supporting information about the goal. Information resources can include inline text commentary and links to web resources.</t>
+  </si>
+  <si>
+    <t>PlanDefinition.goal.target</t>
+  </si>
+  <si>
+    <t>目標のターゲット結果 / Target outcome for the goal</t>
+  </si>
+  <si>
+    <t>何をすべきか、どの時間枠内で何をすべきかを示します。 / Indicates what should be done and within what timeframe.</t>
+  </si>
+  <si>
+    <t>PlanDefinition.goal.target.id</t>
+  </si>
+  <si>
+    <t>PlanDefinition.goal.target.extension</t>
+  </si>
+  <si>
+    <t>PlanDefinition.goal.target.modifierExtension</t>
+  </si>
+  <si>
+    <t>PlanDefinition.goal.target.measure</t>
+  </si>
+  <si>
+    <t>値を追跡するパラメーター / The parameter whose value is to be tracked</t>
+  </si>
+  <si>
+    <t>値を追跡するパラメーター、例えば体重、血圧、またはヘモグロビンA1Cレベル。 / The parameter whose value is to be tracked, e.g. body weight, blood pressure, or hemoglobin A1c level.</t>
+  </si>
+  <si>
+    <t>目標の達成を決定するために追跡できるパラメーターの種類を識別します。 / Identifies types of parameters that can be tracked to determine goal achievement.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.3.0</t>
+  </si>
+  <si>
+    <t>PlanDefinition.goal.target.detail[x]</t>
+  </si>
+  <si>
+    <t>Quantity
+RangeCodeableConcept</t>
+  </si>
+  <si>
+    <t>達成される目標値 / The target value to be achieved</t>
+  </si>
+  <si>
+    <t>ゴールの達成を示す測定の目標値。例えば150ポンドや7.0%、または医薬品品質の場合はNMT 0.6%、澄明な溶液など。範囲の上限または下限、あるいは両方を指定できます。下限値がない場合、上限値以下の任意の値でゴールが達成されることを示します。同様に、上限値がない場合、下限値以上の任意の値でゴールが達成されることを示します。 / The target value of the measure to be achieved to signify fulfillment of the goal, e.g. 150 pounds or 7.0%, or in the case of pharmaceutical quality - NMT 0.6%, Clear solution, etc. Either the high or low or both values of the range can be specified. When a low value is missing, it indicates that the goal is achieved at any value at or below the high value. Similarly, if the high value is missing, it indicates that the goal is achieved at any value at or above the low value.</t>
+  </si>
+  <si>
+    <t>PlanDefinition.goal.target.due</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duration
+</t>
+  </si>
+  <si>
+    <t>内部のゴールに到達します / Reach goal within</t>
+  </si>
+  <si>
+    <t>ゴールを満たすべき目標の開始後の時間枠を示します。 / Indicates the timeframe after the start of the goal in which the goal should be met.</t>
+  </si>
+  <si>
+    <t>PlanDefinition.action</t>
+  </si>
+  <si>
+    <t>計画によって定義されたアクション / Action defined by the plan</t>
+  </si>
+  <si>
+    <t>プランの一部として実行されるアクションまたはアクションのグループ。例えば、臨床ケアでは、特定の適応薬の処方や、必要に応じた特定の検査の実施がアクションとなります。医薬品品質では、品質仕様で定義された医薬品に対して実施する必要がある試験がアクションとなります。 / An action or group of actions to be taken as part of the plan. For example, in clinical care, an action would be to prescribe a particular indicated medication, or perform a particular test as appropriate. In pharmaceutical quality, an action would be the test that needs to be performed on a drug product as defined in the quality specification.</t>
+  </si>
+  <si>
+    <t>ここで定義されている多くの要素とActivitydefinitionリソースの間には重複していることに注意してください。Activity -Definitionが参照される場合（定義要素を使用）、計画の重複要素は、特定の要素に特に文書化されていない限り、参照されるActivity -Definitionの内容をオーバーライドします。詳細については、Plandfinitionリソースを参照してください。 / Note that there is overlap between many of the elements defined here and the ActivityDefinition resource. When an ActivityDefinition is referenced (using the definition element), the overlapping elements in the plan override the content of the referenced ActivityDefinition unless otherwise documented in the specific elements. See the PlanDefinition resource for more detailed information.</t>
+  </si>
+  <si>
+    <t>{Is a contained Definition}</t>
+  </si>
+  <si>
+    <t>Act[classCode=ACT; moodCode=DEFN]</t>
+  </si>
+  <si>
+    <t>PlanDefinition.action.id</t>
+  </si>
+  <si>
+    <t>PlanDefinition.action.extension</t>
+  </si>
+  <si>
+    <t>PlanDefinition.action.extension:timingDaysOfCycle</t>
+  </si>
+  <si>
+    <t>timingDaysOfCycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {timing-daysOfCycle|5.2.0}
+</t>
+  </si>
+  <si>
+    <t>Days on which the action should be performed</t>
+  </si>
+  <si>
+    <t>Days of a possibly repeating cycle on which the action is to be performed. The cycle is defined by the first action with a timing element that is a parent of the daysOfCycle.</t>
+  </si>
+  <si>
+    <t>The cycle is defined by a parent/containing action, and the daysOfCycle extension is used on individual actions within that cycle to indicate the days of the cycle on which the actions should be performed.</t>
+  </si>
+  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>PlanDefinition.extension:regimenType</t>
-  </si>
-  <si>
-    <t>regimenType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_PlanDefinition_ChemotherapyRegimen_RegimenType}
-</t>
-  </si>
-  <si>
-    <t>【仮】レジメン種別に関する情報</t>
-  </si>
-  <si>
-    <t>レジメン種別に関する情報を格納するためのExtension。</t>
-  </si>
-  <si>
-    <t>レジメン種別に関する情報を表現する拡張</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>PlanDefinition.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>PlanDefinition.url</t>
-  </si>
-  <si>
-    <t>Canonical identifier for this plan definition, represented as a URI (globally unique)</t>
-  </si>
-  <si>
-    <t>An absolute URI that is used to identify this plan definition when it is referenced in a specification, model, design or an instance; also called its canonical identifier. This SHOULD be globally unique and SHOULD be a literal address at which at which an authoritative instance of this plan definition is (or will be) published. This URL can be the target of a canonical reference. It SHALL remain the same when the plan definition is stored on different servers.</t>
-  </si>
-  <si>
-    <t>Can be a urn:uuid: or a urn:oid: but real http: addresses are preferred.  Multiple instances may share the same URL if they have a distinct version.
-The determination of when to create a new version of a resource (same url, new version) vs. defining a new artifact is up to the author.  Considerations for making this decision are found in [Technical and Business Versions](http://hl7.org/fhir/R4B/resource.html#versions). 
-In some cases, the resource can no longer be found at the stated url, but the url itself cannot change. Implementations can use the [meta.source](http://hl7.org/fhir/R4B/resource.html#meta) element to indicate where the current master source of the resource can be found.</t>
-  </si>
-  <si>
-    <t>Allows the plan definition to be referenced by a single globally unique identifier.</t>
-  </si>
-  <si>
-    <t>Definition.url</t>
-  </si>
-  <si>
-    <t>.identifier[scope=BUSN;reliability=ISS]</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>PlanDefinition.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Additional identifier for the plan definition</t>
-  </si>
-  <si>
-    <t>A formal identifier that is used to identify this plan definition when it is represented in other formats, or referenced in a specification, model, design or an instance.</t>
-  </si>
-  <si>
-    <t>Typically, this is used for identifiers that can go in an HL7 V3 II (instance identifier) data type, and can then identify this plan definition outside of FHIR, where it is not possible to use the logical URI.</t>
-  </si>
-  <si>
-    <t>Allows externally provided and/or usable business identifiers to be easily associated with the module.</t>
-  </si>
-  <si>
-    <t>Definition.identifier</t>
-  </si>
-  <si>
-    <t>.identifier</t>
-  </si>
-  <si>
-    <t>no-gen-base</t>
-  </si>
-  <si>
-    <t>PlanDefinition.version</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Business version of the plan definition</t>
-  </si>
-  <si>
-    <t>The identifier that is used to identify this version of the plan definition when it is referenced in a specification, model, design or instance. This is an arbitrary value managed by the plan definition author and is not expected to be globally unique. For example, it might be a timestamp (e.g. yyyymmdd) if a managed version is not available. There is also no expectation that versions can be placed in a lexicographical sequence. To provide a version consistent with the Decision Support Service specification, use the format Major.Minor.Revision (e.g. 1.0.0). For more information on versioning knowledge assets, refer to the Decision Support Service specification. Note that a version is required for non-experimental active artifacts.</t>
-  </si>
-  <si>
-    <t>There may be different plan definition instances that have the same identifier but different versions.  The version can be appended to the url in a reference to allow a reference to a particular business version of the plan definition with the format [url]|[version].</t>
-  </si>
-  <si>
-    <t>Definition.version</t>
-  </si>
-  <si>
-    <t>N/A (to add?)</t>
-  </si>
-  <si>
-    <t>FiveWs.version</t>
-  </si>
-  <si>
-    <t>PlanDefinition.name</t>
-  </si>
-  <si>
-    <t>Name for this plan definition (computer friendly)</t>
-  </si>
-  <si>
-    <t>A natural language name identifying the plan definition. This name should be usable as an identifier for the module by machine processing applications such as code generation.</t>
-  </si>
-  <si>
-    <t>The name is not expected to be globally unique. The name should be a simple alphanumeric type name to ensure that it is machine-processing friendly.</t>
-  </si>
-  <si>
-    <t>Support human navigation and code generation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cnl-0
-</t>
-  </si>
-  <si>
-    <t>PlanDefinition.title</t>
-  </si>
-  <si>
-    <t>Name for this plan definition (human friendly)</t>
-  </si>
-  <si>
-    <t>A short, descriptive, user-friendly title for the plan definition.</t>
-  </si>
-  <si>
-    <t>This name does not need to be machine-processing friendly and may contain punctuation, white-space, etc.</t>
-  </si>
-  <si>
-    <t>Definition.title</t>
-  </si>
-  <si>
-    <t>.title</t>
-  </si>
-  <si>
-    <t>PlanDefinition.subtitle</t>
-  </si>
-  <si>
-    <t>Subordinate title of the plan definition</t>
-  </si>
-  <si>
-    <t>An explanatory or alternate title for the plan definition giving additional information about its content.</t>
-  </si>
-  <si>
-    <t>PlanDefinition.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>order-set | clinical-protocol | eca-rule | workflow-definition</t>
-  </si>
-  <si>
-    <t>A high-level category for the plan definition that distinguishes the kinds of systems that would be interested in the plan definition.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>The type of PlanDefinition.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/plan-definition-type|4.3.0</t>
-  </si>
-  <si>
-    <t>PlanDefinition.status</t>
-  </si>
-  <si>
-    <t>draft | active | retired | unknown</t>
-  </si>
-  <si>
-    <t>The status of this plan definition. Enables tracking the life-cycle of the content.</t>
-  </si>
-  <si>
-    <t>Allows filtering of plan definitions that are appropriate for use versus not.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>The lifecycle status of an artifact.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/publication-status|4.3.0</t>
-  </si>
-  <si>
-    <t>Definition.status {different ValueSet}</t>
-  </si>
-  <si>
-    <t>.status</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>PlanDefinition.experimental</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>For testing purposes, not real usage</t>
-  </si>
-  <si>
-    <t>A Boolean value to indicate that this plan definition is authored for testing purposes (or education/evaluation/marketing) and is not intended to be used for genuine usage.</t>
-  </si>
-  <si>
-    <t>Enables experimental content to be developed following the same lifecycle that would be used for a production-level plan definition.</t>
-  </si>
-  <si>
-    <t>Definition.experimental</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>PlanDefinition.subject[x]</t>
-  </si>
-  <si>
-    <t>CodeableConcept
-Reference(Group|4.3.0)canonical(MedicinalProductDefinition|4.3.0|SubstanceDefinition|4.3.0|AdministrableProductDefinition|4.3.0|ManufacturedItemDefinition|4.3.0|PackagedProductDefinition|4.3.0)</t>
-  </si>
-  <si>
-    <t>Type of individual the plan definition is focused on</t>
-  </si>
-  <si>
-    <t>A code, group definition, or canonical reference that describes  or identifies the intended subject of the plan definition. Canonical references are allowed to support the definition of protocols for drug and substance quality specifications, and is allowed to reference a MedicinalProductDefinition, SubstanceDefinition, AdministrableProductDefinition, ManufacturedItemDefinition, or PackagedProductDefinition resource.</t>
-  </si>
-  <si>
-    <t>Note that the choice of canonical for the subject element was introduced in R4B to support pharmaceutical quality use cases. To ensure as much backwards-compatibility as possible, it is recommended to only use the new canonical type with these use cases.</t>
-  </si>
-  <si>
-    <t>Patient</t>
-  </si>
-  <si>
-    <t>The possible types of subjects for a plan definition (E.g. Patient, Practitioner, Organization, Location, etc.).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/subject-type|4.3.0</t>
-  </si>
-  <si>
-    <t>Definition.subject</t>
-  </si>
-  <si>
-    <t>PlanDefinition.date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revision Date
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Date last changed</t>
-  </si>
-  <si>
-    <t>The date  (and optionally time) when the plan definition was published. The date must change when the business version changes and it must change if the status code changes. In addition, it should change when the substantive content of the plan definition changes.</t>
-  </si>
-  <si>
-    <t>Note that this is not the same as the resource last-modified-date, since the resource may be a secondary representation of the plan definition. Additional specific dates may be added as extensions or be found by consulting Provenances associated with past versions of the resource.</t>
-  </si>
-  <si>
-    <t>Definition.date</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>PlanDefinition.publisher</t>
-  </si>
-  <si>
-    <t>Name of the publisher (organization or individual)</t>
-  </si>
-  <si>
-    <t>The name of the organization or individual that published the plan definition.</t>
-  </si>
-  <si>
-    <t>Usually an organization but may be an individual. The publisher (or steward) of the plan definition is the organization or individual primarily responsible for the maintenance and upkeep of the plan definition. This is not necessarily the same individual or organization that developed and initially authored the content. The publisher is the primary point of contact for questions or issues with the plan definition. This item SHOULD be populated unless the information is available from context.</t>
-  </si>
-  <si>
-    <t>Helps establish the "authority/credibility" of the plan definition.  May also allow for contact.</t>
-  </si>
-  <si>
-    <t>Definition.publisher</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=AUT].role</t>
-  </si>
-  <si>
-    <t>FiveWs.witness</t>
-  </si>
-  <si>
-    <t>PlanDefinition.contact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ContactDetail
-</t>
-  </si>
-  <si>
-    <t>Contact details for the publisher</t>
-  </si>
-  <si>
-    <t>Contact details to assist a user in finding and communicating with the publisher.</t>
-  </si>
-  <si>
-    <t>May be a web site, an email address, a telephone number, etc.</t>
-  </si>
-  <si>
-    <t>Definition.contact</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=CALLBCK].role</t>
-  </si>
-  <si>
-    <t>PlanDefinition.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">markdown
-</t>
-  </si>
-  <si>
-    <t>Natural language description of the plan definition</t>
-  </si>
-  <si>
-    <t>A free text natural language description of the plan definition from a consumer's perspective.</t>
-  </si>
-  <si>
-    <t>This description can be used to capture details such as why the plan definition was built, comments about misuse, instructions for clinical use and interpretation, literature references, examples from the paper world, etc. It is not a rendering of the plan definition as conveyed in the 'text' field of the resource itself. This item SHOULD be populated unless the information is available from context (e.g. the language of the plan definition is presumed to be the predominant language in the place the plan definition was created).</t>
-  </si>
-  <si>
-    <t>Definition.description</t>
-  </si>
-  <si>
-    <t>.text</t>
-  </si>
-  <si>
-    <t>PlanDefinition.useContext</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UsageContext
-</t>
-  </si>
-  <si>
-    <t>【仮】対象疾患</t>
-  </si>
-  <si>
-    <t>The content was developed with a focus and intent of supporting the contexts that are listed. These contexts may be general categories (gender, age, ...) or may be references to specific programs (insurance plans, studies, ...) and may be used to assist with indexing and searching for appropriate plan definition instances.</t>
-  </si>
-  <si>
-    <t>When multiple useContexts are specified, there is no expectation that all or any of the contexts apply.</t>
-  </si>
-  <si>
-    <t>Assist in searching for appropriate content.</t>
-  </si>
-  <si>
-    <t>Definition.useContext</t>
-  </si>
-  <si>
-    <t>PlanDefinition.jurisdiction</t>
-  </si>
-  <si>
-    <t>Intended jurisdiction for plan definition (if applicable)</t>
-  </si>
-  <si>
-    <t>A legal or geographic region in which the plan definition is intended to be used.</t>
-  </si>
-  <si>
-    <t>It may be possible for the plan definition to be used in jurisdictions other than those for which it was originally designed or intended.</t>
-  </si>
-  <si>
-    <t>Countries and regions within which this artifact is targeted for use.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.3.0</t>
-  </si>
-  <si>
-    <t>Definition.jurisdiction</t>
-  </si>
-  <si>
-    <t>PlanDefinition.purpose</t>
-  </si>
-  <si>
-    <t>Why this plan definition is defined</t>
-  </si>
-  <si>
-    <t>Explanation of why this plan definition is needed and why it has been designed as it has.</t>
-  </si>
-  <si>
-    <t>This element does not describe the usage of the plan definition. Instead, it provides traceability of ''why'' the resource is either needed or ''why'' it is defined as it is.  This may be used to point to source materials or specifications that drove the structure of this plan definition.</t>
-  </si>
-  <si>
-    <t>Definition.purpose</t>
-  </si>
-  <si>
-    <t>.reasonCode.text</t>
-  </si>
-  <si>
-    <t>FiveWs.why[x]</t>
-  </si>
-  <si>
-    <t>PlanDefinition.usage</t>
-  </si>
-  <si>
-    <t>Describes the clinical usage of the plan</t>
-  </si>
-  <si>
-    <t>A detailed description of how the plan definition is used from a clinical perspective.</t>
-  </si>
-  <si>
-    <t>PlanDefinition.copyright</t>
-  </si>
-  <si>
-    <t>License
-Restrictions</t>
-  </si>
-  <si>
-    <t>Use and/or publishing restrictions</t>
-  </si>
-  <si>
-    <t>A copyright statement relating to the plan definition and/or its contents. Copyright statements are generally legal restrictions on the use and publishing of the plan definition.</t>
-  </si>
-  <si>
-    <t>Consumers must be able to determine any legal restrictions on the use of the plan definition and/or its content.</t>
-  </si>
-  <si>
-    <t>Definition.copyright</t>
-  </si>
-  <si>
-    <t>PlanDefinition.approvalDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date
-</t>
-  </si>
-  <si>
-    <t>When the plan definition was approved by publisher</t>
-  </si>
-  <si>
-    <t>The date on which the resource content was approved by the publisher. Approval happens once when the content is officially approved for usage.</t>
-  </si>
-  <si>
-    <t>The 'date' element may be more recent than the approval date because of minor changes or editorial corrections.</t>
-  </si>
-  <si>
-    <t>Definition.approvalDate</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="SUBJ"].act[classCode=CACT;moodCode=EVN;code="approval"].effectiveTime</t>
-  </si>
-  <si>
-    <t>PlanDefinition.lastReviewDate</t>
-  </si>
-  <si>
-    <t>When the plan definition was last reviewed</t>
-  </si>
-  <si>
-    <t>The date on which the resource content was last reviewed. Review happens periodically after approval but does not change the original approval date.</t>
-  </si>
-  <si>
-    <t>If specified, this date follows the original approval date.</t>
-  </si>
-  <si>
-    <t>Gives a sense of how "current" the content is.  Resources that have not been reviewed in a long time may have a risk of being less appropriate/relevant.</t>
-  </si>
-  <si>
-    <t>Definition.lastReviewDate</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="SUBJ"; subsetCode="RECENT"].act[classCode=CACT;moodCode=EVN;code="review"].effectiveTime</t>
-  </si>
-  <si>
-    <t>PlanDefinition.effectivePeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>When the plan definition is expected to be used</t>
-  </si>
-  <si>
-    <t>The period during which the plan definition content was or is planned to be in active use.</t>
-  </si>
-  <si>
-    <t>The effective period for a plan definition  determines when the content is applicable for usage and is independent of publication and review dates. For example, a measure intended to be used for the year 2016 might be published in 2015.</t>
-  </si>
-  <si>
-    <t>Allows establishing a transition before a resource comes into effect and also allows for a sunsetting  process when new versions of the plan definition are or are expected to be used instead.</t>
-  </si>
-  <si>
-    <t>Definition.effectivePeriod</t>
-  </si>
-  <si>
-    <t>PlanDefinition.topic</t>
-  </si>
-  <si>
-    <t>E.g. Education, Treatment, Assessment</t>
-  </si>
-  <si>
-    <t>Descriptive topics related to the content of the plan definition. Topics provide a high-level categorization of the definition that can be useful for filtering and searching.</t>
-  </si>
-  <si>
-    <t>Repositories must be able to determine how to categorize the plan definition so that it can be found by topical searches.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>High-level categorization of the definition, used for searching, sorting, and filtering.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/definition-topic|4.3.0</t>
-  </si>
-  <si>
-    <t>Definition.subject[x]</t>
-  </si>
-  <si>
-    <t>PlanDefinition.author</t>
-  </si>
-  <si>
-    <t>Who authored the content</t>
-  </si>
-  <si>
-    <t>An individiual or organization primarily involved in the creation and maintenance of the content.</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=AUT]</t>
-  </si>
-  <si>
-    <t>PlanDefinition.editor</t>
-  </si>
-  <si>
-    <t>Who edited the content</t>
-  </si>
-  <si>
-    <t>An individual or organization primarily responsible for internal coherence of the content.</t>
-  </si>
-  <si>
-    <t>PlanDefinition.reviewer</t>
-  </si>
-  <si>
-    <t>Who reviewed the content</t>
-  </si>
-  <si>
-    <t>An individual or organization primarily responsible for review of some aspect of the content.</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=VRF] {not clear whether VRF best corresponds to reviewer or endorser}</t>
-  </si>
-  <si>
-    <t>PlanDefinition.endorser</t>
-  </si>
-  <si>
-    <t>Who endorsed the content</t>
-  </si>
-  <si>
-    <t>An individual or organization responsible for officially endorsing the content for use in some setting.</t>
-  </si>
-  <si>
-    <t>PlanDefinition.relatedArtifact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RelatedArtifact
-</t>
-  </si>
-  <si>
-    <t>Additional documentation, citations</t>
-  </si>
-  <si>
-    <t>Related artifacts such as additional documentation, justification, or bibliographic references.</t>
-  </si>
-  <si>
-    <t>Each related artifact is either an attachment, or a reference to another resource, but not both.</t>
-  </si>
-  <si>
-    <t>Plan definitions must be able to provide enough information for consumers of the content (and/or interventions or results produced by the content) to be able to determine and understand the justification for and evidence in support of the content.</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=DOC,RSON,PREV, DRIV, USE, COMP] {successor would be PREV w/ inversionInd=true; No support for citation}</t>
-  </si>
-  <si>
-    <t>PlanDefinition.library</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(Library|4.3.0)
-</t>
-  </si>
-  <si>
-    <t>Logic used by the plan definition</t>
-  </si>
-  <si>
-    <t>A reference to a Library resource containing any formal logic used by the plan definition.</t>
-  </si>
-  <si>
-    <t>PlanDefinition.goal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>What the plan is trying to accomplish</t>
-  </si>
-  <si>
-    <t>A goal describes an expected outcome that activities within the plan are intended to achieve. For example, weight loss, restoring an activity of daily living, obtaining herd immunity via immunization, meeting a process improvement objective, meeting the acceptance criteria for a test as specified by a quality specification, etc.</t>
-  </si>
-  <si>
-    <t>Goal information needs to be captured for order sets, protocols, and care plan definitions to better describe the objectives of the protocol activities and to guide the creation of specific goals within the derived care plans and orders.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-</t>
-  </si>
-  <si>
-    <t>PlanDefinition.goal.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>PlanDefinition.goal.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>PlanDefinition.goal.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>PlanDefinition.goal.category</t>
-  </si>
-  <si>
-    <t>E.g. Treatment, dietary, behavioral</t>
-  </si>
-  <si>
-    <t>Indicates a category the goal falls within.</t>
-  </si>
-  <si>
-    <t>Example codes for grouping goals for filtering or presentation.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/goal-category|4.3.0</t>
-  </si>
-  <si>
-    <t>PlanDefinition.goal.description</t>
-  </si>
-  <si>
-    <t>Code or text describing the goal</t>
-  </si>
-  <si>
-    <t>Human-readable and/or coded description of a specific desired objective of care, such as "control blood pressure" or "negotiate an obstacle course" or "dance with child at wedding".</t>
-  </si>
-  <si>
-    <t>If no code is available, use CodeableConcept.text.</t>
-  </si>
-  <si>
-    <t>Describes goals that can be achieved.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.3.0</t>
-  </si>
-  <si>
-    <t>PlanDefinition.goal.priority</t>
-  </si>
-  <si>
-    <t>high-priority | medium-priority | low-priority</t>
-  </si>
-  <si>
-    <t>Identifies the expected level of importance associated with reaching/sustaining the defined goal.</t>
-  </si>
-  <si>
-    <t>Indicates the level of importance associated with reaching or sustaining a goal.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/goal-priority|4.3.0</t>
-  </si>
-  <si>
-    <t>PlanDefinition.goal.start</t>
-  </si>
-  <si>
-    <t>When goal pursuit begins</t>
-  </si>
-  <si>
-    <t>The event after which the goal should begin being pursued.</t>
-  </si>
-  <si>
-    <t>Identifies the types of events that might trigger the start of a goal.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/goal-start-event|4.3.0</t>
-  </si>
-  <si>
-    <t>PlanDefinition.goal.addresses</t>
-  </si>
-  <si>
-    <t>What does the goal address</t>
-  </si>
-  <si>
-    <t>Identifies problems, conditions, issues, or concerns the goal is intended to address.</t>
-  </si>
-  <si>
-    <t>Identifies problems, conditions, issues, or concerns that goals may address.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code|4.3.0</t>
-  </si>
-  <si>
-    <t>PlanDefinition.goal.documentation</t>
-  </si>
-  <si>
-    <t>Supporting documentation for the goal</t>
-  </si>
-  <si>
-    <t>Didactic or other informational resources associated with the goal that provide further supporting information about the goal. Information resources can include inline text commentary and links to web resources.</t>
-  </si>
-  <si>
-    <t>PlanDefinition.goal.target</t>
-  </si>
-  <si>
-    <t>Target outcome for the goal</t>
-  </si>
-  <si>
-    <t>Indicates what should be done and within what timeframe.</t>
-  </si>
-  <si>
-    <t>PlanDefinition.goal.target.id</t>
-  </si>
-  <si>
-    <t>PlanDefinition.goal.target.extension</t>
-  </si>
-  <si>
-    <t>PlanDefinition.goal.target.modifierExtension</t>
-  </si>
-  <si>
-    <t>PlanDefinition.goal.target.measure</t>
-  </si>
-  <si>
-    <t>The parameter whose value is to be tracked</t>
-  </si>
-  <si>
-    <t>The parameter whose value is to be tracked, e.g. body weight, blood pressure, or hemoglobin A1c level.</t>
-  </si>
-  <si>
-    <t>Identifies types of parameters that can be tracked to determine goal achievement.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.3.0</t>
-  </si>
-  <si>
-    <t>PlanDefinition.goal.target.detail[x]</t>
-  </si>
-  <si>
-    <t>Quantity
-RangeCodeableConcept</t>
-  </si>
-  <si>
-    <t>The target value to be achieved</t>
-  </si>
-  <si>
-    <t>The target value of the measure to be achieved to signify fulfillment of the goal, e.g. 150 pounds or 7.0%, or in the case of pharmaceutical quality - NMT 0.6%, Clear solution, etc. Either the high or low or both values of the range can be specified. When a low value is missing, it indicates that the goal is achieved at any value at or below the high value. Similarly, if the high value is missing, it indicates that the goal is achieved at any value at or above the low value.</t>
-  </si>
-  <si>
-    <t>PlanDefinition.goal.target.due</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duration
-</t>
-  </si>
-  <si>
-    <t>Reach goal within</t>
-  </si>
-  <si>
-    <t>Indicates the timeframe after the start of the goal in which the goal should be met.</t>
-  </si>
-  <si>
-    <t>PlanDefinition.action</t>
-  </si>
-  <si>
-    <t>Action defined by the plan</t>
-  </si>
-  <si>
-    <t>An action or group of actions to be taken as part of the plan. For example, in clinical care, an action would be to prescribe a particular indicated medication, or perform a particular test as appropriate. In pharmaceutical quality, an action would be the test that needs to be performed on a drug product as defined in the quality specification.</t>
-  </si>
-  <si>
-    <t>Note that there is overlap between many of the elements defined here and the ActivityDefinition resource. When an ActivityDefinition is referenced (using the definition element), the overlapping elements in the plan override the content of the referenced ActivityDefinition unless otherwise documented in the specific elements. See the PlanDefinition resource for more detailed information.</t>
-  </si>
-  <si>
-    <t>{Is a contained Definition}</t>
-  </si>
-  <si>
-    <t>Act[classCode=ACT; moodCode=DEFN]</t>
-  </si>
-  <si>
-    <t>PlanDefinition.action.id</t>
-  </si>
-  <si>
-    <t>PlanDefinition.action.extension</t>
-  </si>
-  <si>
-    <t>PlanDefinition.action.extension:timingDaysOfCycle</t>
-  </si>
-  <si>
-    <t>timingDaysOfCycle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {timing-daysOfCycle|5.2.0}
-</t>
-  </si>
-  <si>
-    <t>Days on which the action should be performed</t>
-  </si>
-  <si>
-    <t>Days of a possibly repeating cycle on which the action is to be performed. The cycle is defined by the first action with a timing element that is a parent of the daysOfCycle.</t>
-  </si>
-  <si>
-    <t>The cycle is defined by a parent/containing action, and the daysOfCycle extension is used on individual actions within that cycle to indicate the days of the cycle on which the actions should be performed.</t>
-  </si>
-  <si>
     <t>PlanDefinition.action.modifierExtension</t>
   </si>
   <si>
     <t>PlanDefinition.action.prefix</t>
   </si>
   <si>
-    <t>User-visible prefix for the action (e.g. 1. or A.)</t>
-  </si>
-  <si>
-    <t>A user-visible prefix for the action.</t>
+    <t>アクションのユーザー可視プレフィックス（例：1またはA） / User-visible prefix for the action (e.g. 1. or A.)</t>
+  </si>
+  <si>
+    <t>アクションのユーザー可視プレフィックス。 / A user-visible prefix for the action.</t>
   </si>
   <si>
     <t>PlanDefinition.action.title</t>
   </si>
   <si>
-    <t>User-visible title</t>
-  </si>
-  <si>
-    <t>The textual description of the action displayed to a user. For example, when the action is a test to be performed, the title would be the title of the test such as Assay by HPLC.</t>
+    <t>ユーザー可視タイトル / User-visible title</t>
+  </si>
+  <si>
+    <t>ユーザーに表示されるアクションのテキスト説明。例えば、アクションが実施すべき試験の場合、タイトルはHPLCによるアッセイなどの試験のタイトルになります。 / The textual description of the action displayed to a user. For example, when the action is a test to be performed, the title would be the title of the test such as Assay by HPLC.</t>
   </si>
   <si>
     <t>PlanDefinition.action.description</t>
   </si>
   <si>
-    <t>Brief description of the action</t>
-  </si>
-  <si>
-    <t>A brief description of the action used to provide a summary to display to the user.</t>
+    <t>アクションの簡単な説明 / Brief description of the action</t>
+  </si>
+  <si>
+    <t>ユーザーに表示するための要約を提供するために使用されるアクションの簡単な説明。 / A brief description of the action used to provide a summary to display to the user.</t>
   </si>
   <si>
     <t>PlanDefinition.action.textEquivalent</t>
   </si>
   <si>
-    <t>Static text equivalent of the action, used if the dynamic aspects cannot be interpreted by the receiving system</t>
-  </si>
-  <si>
-    <t>A text equivalent of the action to be performed. This provides a human-interpretable description of the action when the definition is consumed by a system that might not be capable of interpreting it dynamically.</t>
+    <t>動的な側面を受信システムによって解釈できない場合に使用されるアクションに相当する静的テキスト / Static text equivalent of the action, used if the dynamic aspects cannot be interpreted by the receiving system</t>
+  </si>
+  <si>
+    <t>実行されるアクションに相当するテキスト。これにより、定義が動的に解釈できないシステムによって消費される場合、アクションの人間が解釈できる説明が提供されます。 / A text equivalent of the action to be performed. This provides a human-interpretable description of the action when the definition is consumed by a system that might not be capable of interpreting it dynamically.</t>
   </si>
   <si>
     <t>PlanDefinition.action.priority</t>
   </si>
   <si>
-    <t>routine | urgent | asap | stat</t>
-  </si>
-  <si>
-    <t>Indicates how quickly the action should be addressed with respect to other actions.</t>
-  </si>
-  <si>
-    <t>Identifies the level of importance to be assigned to actioning the request.</t>
+    <t>ルーチン|緊急|できるだけ早く|統計 / routine | urgent | asap | stat</t>
+  </si>
+  <si>
+    <t>他のアクションに関して、アクションがどれだけ速く対処されるべきかを示します。 / Indicates how quickly the action should be addressed with respect to other actions.</t>
+  </si>
+  <si>
+    <t>リクエストの実行に割り当てられる重要性のレベルを特定します。 / Identifies the level of importance to be assigned to actioning the request.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/request-priority|4.3.0</t>
@@ -1395,13 +1403,13 @@
     <t>PlanDefinition.action.code</t>
   </si>
   <si>
-    <t>Code representing the meaning of the action or sub-actions</t>
-  </si>
-  <si>
-    <t>A code that provides a meaning, grouping, or classification for the action or action group. For example, a section may have a LOINC code for the section of a documentation template. In pharmaceutical quality, an action (Test) such as pH could be classified as a physical property.</t>
-  </si>
-  <si>
-    <t>Provides examples of actions to be performed.</t>
+    <t>アクションまたはサブアクションの意味を表すコード / Code representing the meaning of the action or sub-actions</t>
+  </si>
+  <si>
+    <t>アクションまたはアクショングループの意味、グループ化、または分類を提供するコード。例えば、セクションにはドキュメントテンプレートのセクション用のLOINCコードがある場合があります。医薬品品質では、pHなどのアクション（試験）は物理的特性として分類される場合があります。 / A code that provides a meaning, grouping, or classification for the action or action group. For example, a section may have a LOINC code for the section of a documentation template. In pharmaceutical quality, an action (Test) such as pH could be classified as a physical property.</t>
+  </si>
+  <si>
+    <t>実行されるアクションの例を提供する。 / Provides examples of actions to be performed.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/action-code|4.3.0</t>
@@ -1413,16 +1421,16 @@
     <t>PlanDefinition.action.reason</t>
   </si>
   <si>
-    <t>Why the action should be performed</t>
-  </si>
-  <si>
-    <t>A description of why this action is necessary or appropriate.</t>
-  </si>
-  <si>
-    <t>This is different than the clinical evidence documentation, it's an actual business description of the reason for performing the action.</t>
-  </si>
-  <si>
-    <t>Provides examples of reasons for actions to be performed.</t>
+    <t>アクションを実行する必要がある理由 / Why the action should be performed</t>
+  </si>
+  <si>
+    <t>このアクションが必要または適切である理由の説明。 / A description of why this action is necessary or appropriate.</t>
+  </si>
+  <si>
+    <t>これは臨床証拠の文書とは異なり、アクションを実行する理由の実際のビジネス記述です。 / This is different than the clinical evidence documentation, it's an actual business description of the reason for performing the action.</t>
+  </si>
+  <si>
+    <t>アクションを実行する理由の例を提供する。 / Provides examples of reasons for actions to be performed.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/action-reason-code|4.3.0</t>
@@ -1434,19 +1442,19 @@
     <t>PlanDefinition.action.documentation</t>
   </si>
   <si>
-    <t>Supporting documentation for the intended performer of the action</t>
-  </si>
-  <si>
-    <t>Didactic or other informational resources associated with the action that can be provided to the CDS recipient. Information resources can include inline text commentary and links to web resources.</t>
+    <t>意図したアクションのパフォーマーのためのドキュメントをサポートします / Supporting documentation for the intended performer of the action</t>
+  </si>
+  <si>
+    <t>CDS受信者に提供できるアクションに関連する教訓的またはその他の情報リソース。情報リソースには、インラインテキストの解説とWebリソースへのリンクを含めることができます。 / Didactic or other informational resources associated with the action that can be provided to the CDS recipient. Information resources can include inline text commentary and links to web resources.</t>
   </si>
   <si>
     <t>PlanDefinition.action.goalId</t>
   </si>
   <si>
-    <t>What goals this action supports</t>
-  </si>
-  <si>
-    <t>Identifies goals that this action supports. The reference must be to a goal element defined within this plan definition. In pharmaceutical quality, a goal represents acceptance criteria (Goal) for a given action (Test), so the goalId would be the unique id of a defined goal element establishing the acceptance criteria for the action.</t>
+    <t>このアクションがサポートする目標 / What goals this action supports</t>
+  </si>
+  <si>
+    <t>このアクションがサポートするゴールを識別します。参照は、このプラン定義内で定義されたゴール要素である必要があります。医薬品品質では、ゴールは特定のアクション（試験）の受入基準（Goal）を表すため、goalIdはアクションの受入基準を確立する定義済みゴール要素の一意のIDになります。 / Identifies goals that this action supports. The reference must be to a goal element defined within this plan definition. In pharmaceutical quality, a goal represents acceptance criteria (Goal) for a given action (Test), so the goalId would be the unique id of a defined goal element establishing the acceptance criteria for the action.</t>
   </si>
   <si>
     <t>PlanDefinition.action.subject[x]</t>
@@ -1456,17 +1464,18 @@
 Reference(Group|4.3.0)canonical</t>
   </si>
   <si>
-    <t>Type of individual the action is focused on</t>
-  </si>
-  <si>
-    <t>A code, group definition, or canonical reference that describes the intended subject of the action and its children, if any. Canonical references are allowed to support the definition of protocols for drug and substance quality specifications, and is allowed to reference a MedicinalProductDefinition, SubstanceDefinition, AdministrableProductDefinition, ManufacturedItemDefinition, or PackagedProductDefinition resource.</t>
-  </si>
-  <si>
-    <t>The subject of an action overrides the subject at a parent action or on the root of the PlanDefinition if specified.
+    <t>個人のタイプアクションが焦点を合わせています / Type of individual the action is focused on</t>
+  </si>
+  <si>
+    <t>アクションとその子要素（存在する場合）の対象となる主題を記述するコード、グループ定義、またはカノニカル参照。カノニカル参照は、医薬品および物質の品質仕様のプロトコル定義をサポートするために許可されており、MedicinalProductDefinition、SubstanceDefinition、AdministrableProductDefinition、ManufacturedItemDefinition、またはPackagedProductDefinitionリソースを参照できます。 / A code, group definition, or canonical reference that describes the intended subject of the action and its children, if any. Canonical references are allowed to support the definition of protocols for drug and substance quality specifications, and is allowed to reference a MedicinalProductDefinition, SubstanceDefinition, AdministrableProductDefinition, ManufacturedItemDefinition, or PackagedProductDefinition resource.</t>
+  </si>
+  <si>
+    <t>アクションの主題は、指定されている場合、親のアクションまたはプランディングのルートで被験者を無効にします。
+さらに、被験者は実現中に解決する必要があるため、アクション（またはアクションによって参照されるアクティビティデファイニング）での被験者の使用は、コンテキストおよびタイプで提供された被験者のセットに基づいて解決します（つまり、患者の被験者はタイプの患者のリソース）。 / The subject of an action overrides the subject at a parent action or on the root of the PlanDefinition if specified.
 In addition, because the subject needs to be resolved during realization, use of subjects in actions (or in the ActivityDefinition referenced by the action) resolves based on the set of subjects supplied in context and by type (i.e. the patient subject would resolve to a resource of type Patient).</t>
   </si>
   <si>
-    <t>Multiple steps in a protocol often have different groups of steps that are focused on testing different things. The subject of an action specifies the focus of the action and any child actions.</t>
+    <t>プロトコルの複数のステップには、さまざまなもののテストに焦点を当てたさまざまなステップのグループがあります。アクションの主題は、アクションの焦点と子どもの行動を指定します。 / Multiple steps in a protocol often have different groups of steps that are focused on testing different things. The subject of an action specifies the focus of the action and any child actions.</t>
   </si>
   <si>
     <t>PlanDefinition.action.trigger</t>
@@ -1476,22 +1485,22 @@
 </t>
   </si>
   <si>
-    <t>When the action should be triggered</t>
-  </si>
-  <si>
-    <t>A description of when the action should be triggered.</t>
+    <t>アクションをトリガーする場合 / When the action should be triggered</t>
+  </si>
+  <si>
+    <t>アクションをトリガーする時期の説明。 / A description of when the action should be triggered.</t>
   </si>
   <si>
     <t>PlanDefinition.action.condition</t>
   </si>
   <si>
-    <t>Whether or not the action is applicable</t>
-  </si>
-  <si>
-    <t>An expression that describes applicability criteria or start/stop conditions for the action.</t>
-  </si>
-  <si>
-    <t>When multiple conditions of the same kind are present, the effects are combined using AND semantics, so the overall condition is true only if all the conditions are true.</t>
+    <t>アクションが適用されるかどうか / Whether or not the action is applicable</t>
+  </si>
+  <si>
+    <t>アクションの適用性基準または開始/停止条件を説明する式。 / An expression that describes applicability criteria or start/stop conditions for the action.</t>
+  </si>
+  <si>
+    <t>同じ種類の複数の条件が存在する場合、効果は使用され、セマンティクスを使用して結合されるため、すべての条件が真である場合にのみ全体的な条件が当てはまります。 / When multiple conditions of the same kind are present, the effects are combined using AND semantics, so the overall condition is true only if all the conditions are true.</t>
   </si>
   <si>
     <t>PlanDefinition.action.condition.id</t>
@@ -1506,16 +1515,16 @@
     <t>PlanDefinition.action.condition.kind</t>
   </si>
   <si>
-    <t>applicability | start | stop</t>
-  </si>
-  <si>
-    <t>The kind of condition.</t>
-  </si>
-  <si>
-    <t>Applicability criteria are used to determine immediate applicability when a plan definition is applied to a given context. Start and stop criteria are carried through application and used to describe enter/exit criteria for an action.</t>
-  </si>
-  <si>
-    <t>Defines the kinds of conditions that can appear on actions.</t>
+    <t>適用性|開始|止まる / applicability | start | stop</t>
+  </si>
+  <si>
+    <t>種類の状態。 / The kind of condition.</t>
+  </si>
+  <si>
+    <t>適用性基準は、計画定義が特定のコンテキストに適用される場合の即時の適用性を決定するために使用されます。開始基準と停止基準は、アプリケーションを通じて実行され、アクションのENTER/EXIT基準を説明するために使用されます。 / Applicability criteria are used to determine immediate applicability when a plan definition is applied to a given context. Start and stop criteria are carried through application and used to describe enter/exit criteria for an action.</t>
+  </si>
+  <si>
+    <t>アクションに表示される可能性のある条件の種類を定義します。 / Defines the kinds of conditions that can appear on actions.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/action-condition-kind|4.3.0</t>
@@ -1528,13 +1537,13 @@
 </t>
   </si>
   <si>
-    <t>Boolean-valued expression</t>
-  </si>
-  <si>
-    <t>An expression that returns true or false, indicating whether the condition is satisfied.</t>
-  </si>
-  <si>
-    <t>The expression may be inlined or may be a reference to a named expression within a logic library referenced by the library element.</t>
+    <t>ブール値の式 / Boolean-valued expression</t>
+  </si>
+  <si>
+    <t>条件が満たされているかどうかを示す、真または偽を返す式。 / An expression that returns true or false, indicating whether the condition is satisfied.</t>
+  </si>
+  <si>
+    <t>式にインラキングされるか、ライブラリ要素によって参照されるロジックライブラリ内の名前付き式への参照である場合があります。 / The expression may be inlined or may be a reference to a named expression within a logic library referenced by the library element.</t>
   </si>
   <si>
     <t>PlanDefinition.action.input</t>
@@ -1544,31 +1553,31 @@
 </t>
   </si>
   <si>
-    <t>Input data requirements</t>
-  </si>
-  <si>
-    <t>Defines input data requirements for the action.</t>
+    <t>入力データ要件 / Input data requirements</t>
+  </si>
+  <si>
+    <t>アクションの入力データ要件を定義します。 / Defines input data requirements for the action.</t>
   </si>
   <si>
     <t>PlanDefinition.action.output</t>
   </si>
   <si>
-    <t>Output data definition</t>
-  </si>
-  <si>
-    <t>Defines the outputs of the action, if any.</t>
+    <t>出力データ定義 / Output data definition</t>
+  </si>
+  <si>
+    <t>ある場合は、アクションの出力を定義します。 / Defines the outputs of the action, if any.</t>
   </si>
   <si>
     <t>PlanDefinition.action.relatedAction</t>
   </si>
   <si>
-    <t>Relationship to another action</t>
-  </si>
-  <si>
-    <t>A relationship to another action such as "before" or "30-60 minutes after start of".</t>
-  </si>
-  <si>
-    <t>When an action depends on multiple actions, the meaning is that all actions are dependencies, rather than that any of the actions are a dependency.</t>
+    <t>別のアクションとの関係 / Relationship to another action</t>
+  </si>
+  <si>
+    <t>「前」または「開始後30〜60分」などの別のアクションとの関係。 / A relationship to another action such as "before" or "30-60 minutes after start of".</t>
+  </si>
+  <si>
+    <t>アクションが複数のアクションに依存する場合、意味はすべてのアクションが依存関係であるということです。 / When an action depends on multiple actions, the meaning is that all actions are dependencies, rather than that any of the actions are a dependency.</t>
   </si>
   <si>
     <t>PlanDefinition.action.relatedAction.id</t>
@@ -1583,22 +1592,22 @@
     <t>PlanDefinition.action.relatedAction.actionId</t>
   </si>
   <si>
-    <t>What action is this related to</t>
-  </si>
-  <si>
-    <t>The element id of the related action.</t>
+    <t>これはどのようなアクションに関連していますか / What action is this related to</t>
+  </si>
+  <si>
+    <t>関連するアクションの要素ID。 / The element id of the related action.</t>
   </si>
   <si>
     <t>PlanDefinition.action.relatedAction.relationship</t>
   </si>
   <si>
-    <t>before-start | before | before-end | concurrent-with-start | concurrent | concurrent-with-end | after-start | after | after-end</t>
-  </si>
-  <si>
-    <t>The relationship of this action to the related action.</t>
-  </si>
-  <si>
-    <t>Defines the types of relationships between actions.</t>
+    <t>スタート前|前|終了前|スタートと同時|同時|並行して逆|アフタースタート|後|アフターエンド / before-start | before | before-end | concurrent-with-start | concurrent | concurrent-with-end | after-start | after | after-end</t>
+  </si>
+  <si>
+    <t>このアクションと関連アクションとの関係。 / The relationship of this action to the related action.</t>
+  </si>
+  <si>
+    <t>アクション間の関係のタイプを定義します。 / Defines the types of relationships between actions.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/action-relationship-type|4.3.0</t>
@@ -1611,10 +1620,10 @@
 Range</t>
   </si>
   <si>
-    <t>Time offset for the relationship</t>
-  </si>
-  <si>
-    <t>A duration or range of durations to apply to the relationship. For example, 30-60 minutes before.</t>
+    <t>関係のタイムオフセット / Time offset for the relationship</t>
+  </si>
+  <si>
+    <t>関係に適用する期間または期間の範囲。たとえば、30〜60分前。 / A duration or range of durations to apply to the relationship. For example, 30-60 minutes before.</t>
   </si>
   <si>
     <t>PlanDefinition.action.timing[x]</t>
@@ -1627,7 +1636,7 @@
     <t>【仮】総サイクル（n日サイクルを n回繰り返す等）</t>
   </si>
   <si>
-    <t>An optional value describing when the action should be performed.</t>
+    <t>アクションを実行する必要があることを説明するオプションの値。 / An optional value describing when the action should be performed.</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -1648,10 +1657,10 @@
     <t>PlanDefinition.action.participant</t>
   </si>
   <si>
-    <t>Who should participate in the action</t>
-  </si>
-  <si>
-    <t>Indicates who should participate in performing the action described.</t>
+    <t>誰がアクションに参加すべきか / Who should participate in the action</t>
+  </si>
+  <si>
+    <t>説明されているアクションの実行に誰が参加すべきかを示します。 / Indicates who should participate in performing the action described.</t>
   </si>
   <si>
     <t>.participation[typeCode=PFM]</t>
@@ -1669,13 +1678,13 @@
     <t>PlanDefinition.action.participant.type</t>
   </si>
   <si>
-    <t>patient | practitioner | related-person | device</t>
-  </si>
-  <si>
-    <t>The type of participant in the action.</t>
-  </si>
-  <si>
-    <t>The type of participant for the action.</t>
+    <t>患者|開業医|関連者|デバイス / patient | practitioner | related-person | device</t>
+  </si>
+  <si>
+    <t>アクションの参加者のタイプ。 / The type of participant in the action.</t>
+  </si>
+  <si>
+    <t>アクションの参加者のタイプ。 / The type of participant for the action.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/action-participant-type|4.3.0</t>
@@ -1687,13 +1696,13 @@
     <t>PlanDefinition.action.participant.role</t>
   </si>
   <si>
-    <t>E.g. Nurse, Surgeon, Parent</t>
-  </si>
-  <si>
-    <t>The role the participant should play in performing the described action.</t>
-  </si>
-  <si>
-    <t>Defines roles played by participants for the action.</t>
+    <t>例えば。看護師、外科医、親 / E.g. Nurse, Surgeon, Parent</t>
+  </si>
+  <si>
+    <t>参加者が説明されたアクションを実行する際に果たすべき役割。 / The role the participant should play in performing the described action.</t>
+  </si>
+  <si>
+    <t>アクションのために参加者が演じる役割を定義します。 / Defines roles played by participants for the action.</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/action-participant-role</t>
@@ -1705,13 +1714,13 @@
     <t>PlanDefinition.action.type</t>
   </si>
   <si>
-    <t>create | update | remove | fire-event</t>
-  </si>
-  <si>
-    <t>The type of action to perform (create, update, remove).</t>
-  </si>
-  <si>
-    <t>The type of action to be performed.</t>
+    <t>作成|更新|削除|ファイアイベント / create | update | remove | fire-event</t>
+  </si>
+  <si>
+    <t>実行するアクションの種類（作成、更新、削除）。 / The type of action to perform (create, update, remove).</t>
+  </si>
+  <si>
+    <t>実行されるアクションの種類。 / The type of action to be performed.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/action-type|4.3.0</t>
@@ -1723,13 +1732,13 @@
     <t>PlanDefinition.action.groupingBehavior</t>
   </si>
   <si>
-    <t>visual-group | logical-group | sentence-group</t>
-  </si>
-  <si>
-    <t>Defines the grouping behavior for the action and its children.</t>
-  </si>
-  <si>
-    <t>Defines organization behavior of a group.</t>
+    <t>ビジュアルグループ|論理グループ|文とグループ / visual-group | logical-group | sentence-group</t>
+  </si>
+  <si>
+    <t>アクションとその子供のグループ化行動を定義します。 / Defines the grouping behavior for the action and its children.</t>
+  </si>
+  <si>
+    <t>グループの組織行動を定義します。 / Defines organization behavior of a group.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/action-grouping-behavior|4.3.0</t>
@@ -1738,13 +1747,13 @@
     <t>PlanDefinition.action.selectionBehavior</t>
   </si>
   <si>
-    <t>any | all | all-or-none | exactly-one | at-most-one | one-or-more</t>
-  </si>
-  <si>
-    <t>Defines the selection behavior for the action and its children.</t>
-  </si>
-  <si>
-    <t>Defines selection behavior of a group.</t>
+    <t>任意の|すべて|オールオアノーン|正確に1つ|一つの1つ|1つ以上 / any | all | all-or-none | exactly-one | at-most-one | one-or-more</t>
+  </si>
+  <si>
+    <t>アクションとその子供の選択行動を定義します。 / Defines the selection behavior for the action and its children.</t>
+  </si>
+  <si>
+    <t>グループの選択動作を定義します。 / Defines selection behavior of a group.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/action-selection-behavior|4.3.0</t>
@@ -1753,13 +1762,13 @@
     <t>PlanDefinition.action.requiredBehavior</t>
   </si>
   <si>
-    <t>must | could | must-unless-documented</t>
-  </si>
-  <si>
-    <t>Defines the required behavior for the action.</t>
-  </si>
-  <si>
-    <t>Defines expectations around whether an action or action group is required.</t>
+    <t>マスト||必須ではない文書化 / must | could | must-unless-documented</t>
+  </si>
+  <si>
+    <t>アクションに必要な動作を定義します。 / Defines the required behavior for the action.</t>
+  </si>
+  <si>
+    <t>アクショングループまたはアクショングループが必要かどうかについての期待を定義します。 / Defines expectations around whether an action or action group is required.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/action-required-behavior|4.3.0</t>
@@ -1768,13 +1777,13 @@
     <t>PlanDefinition.action.precheckBehavior</t>
   </si>
   <si>
-    <t>yes | no</t>
-  </si>
-  <si>
-    <t>Defines whether the action should usually be preselected.</t>
-  </si>
-  <si>
-    <t>Defines selection frequency behavior for an action or group.</t>
+    <t>はい|番号 / yes | no</t>
+  </si>
+  <si>
+    <t>通常、アクションを事前に選択する必要があるかどうかを定義します。 / Defines whether the action should usually be preselected.</t>
+  </si>
+  <si>
+    <t>アクションまたはグループの選択頻度の動作を定義します。 / Defines selection frequency behavior for an action or group.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/action-precheck-behavior|4.3.0</t>
@@ -1783,13 +1792,13 @@
     <t>PlanDefinition.action.cardinalityBehavior</t>
   </si>
   <si>
-    <t>single | multiple</t>
-  </si>
-  <si>
-    <t>Defines whether the action can be selected multiple times.</t>
-  </si>
-  <si>
-    <t>Defines behavior for an action or a group for how many times that item may be repeated.</t>
+    <t>シングル|多数 / single | multiple</t>
+  </si>
+  <si>
+    <t>アクションを複数回選択できるかどうかを定義します。 / Defines whether the action can be selected multiple times.</t>
+  </si>
+  <si>
+    <t>アクションまたはグループの動作を定義します。そのアイテムが繰り返される回数について。 / Defines behavior for an action or a group for how many times that item may be repeated.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/action-cardinality-behavior|4.3.0</t>
@@ -1805,10 +1814,10 @@
     <t>【仮】医薬品情報のActivityDefinitionを参照する</t>
   </si>
   <si>
-    <t>A reference to an ActivityDefinition that describes the action to be taken in detail, or a PlanDefinition that describes a series of actions to be taken.</t>
-  </si>
-  <si>
-    <t>Note that the definition is optional, and if no definition is specified, a dynamicValue with a root ($this) path can be used to define the entire resource dynamically.</t>
+    <t>詳細に取得するアクションを説明するアクティビティデフィニッションへの参照、または取得する一連のアクションを説明するプランディング。 / A reference to an ActivityDefinition that describes the action to be taken in detail, or a PlanDefinition that describes a series of actions to be taken.</t>
+  </si>
+  <si>
+    <t>定義はオプションであり、定義が指定されていない場合、ルート（$この）を持つ動的数値を使用して、リソース全体を動的に定義できることに注意してください。 / Note that the definition is optional, and if no definition is specified, a dynamicValue with a root ($this) path can be used to define the entire resource dynamically.</t>
   </si>
   <si>
     <t>Definition.derivedFrom</t>
@@ -1821,25 +1830,25 @@
 </t>
   </si>
   <si>
-    <t>Transform to apply the template</t>
-  </si>
-  <si>
-    <t>A reference to a StructureMap resource that defines a transform that can be executed to produce the intent resource using the ActivityDefinition instance as the input.</t>
-  </si>
-  <si>
-    <t>Note that when a referenced ActivityDefinition also defines a transform, the transform specified here generally takes precedence. In addition, if both a transform and dynamic values are specific, the dynamic values are applied to the result of the transform.</t>
+    <t>テンプレートを適用するために変換します / Transform to apply the template</t>
+  </si>
+  <si>
+    <t>Activitydefinitionインスタンスを入力として使用して、意図リソースを生成するために実行できる変換を定義するStructureMapリソースへの参照。 / A reference to a StructureMap resource that defines a transform that can be executed to produce the intent resource using the ActivityDefinition instance as the input.</t>
+  </si>
+  <si>
+    <t>参照されるActivity -Definitionが変換も定義する場合、ここで指定された変換が一般的に優先されることに注意してください。さらに、変換値と動的値の両方が固有の場合、動的値は変換の結果に適用されます。 / Note that when a referenced ActivityDefinition also defines a transform, the transform specified here generally takes precedence. In addition, if both a transform and dynamic values are specific, the dynamic values are applied to the result of the transform.</t>
   </si>
   <si>
     <t>PlanDefinition.action.dynamicValue</t>
   </si>
   <si>
-    <t>Dynamic aspects of the definition</t>
-  </si>
-  <si>
-    <t>Customizations that should be applied to the statically defined resource. For example, if the dosage of a medication must be computed based on the patient's weight, a customization would be used to specify an expression that calculated the weight, and the path on the resource that would contain the result.</t>
-  </si>
-  <si>
-    <t>Dynamic values are applied in the order in which they are defined in the PlanDefinition resource. Note that when dynamic values are also specified by a referenced ActivityDefinition, the dynamicValues from the ActivityDefinition are applied first, followed by the dynamicValues specified here. In addition, if both a transform and dynamic values are specific, the dynamic values are applied to the result of the transform.</t>
+    <t>定義の動的な側面 / Dynamic aspects of the definition</t>
+  </si>
+  <si>
+    <t>静的に定義されたリソースに適用する必要があるカスタマイズ。たとえば、薬物の投与量を患者の体重に基づいて計算する必要がある場合、カスタマイズを使用して、重量を計算する式と結果を含むリソースの経路を指定するために使用されます。 / Customizations that should be applied to the statically defined resource. For example, if the dosage of a medication must be computed based on the patient's weight, a customization would be used to specify an expression that calculated the weight, and the path on the resource that would contain the result.</t>
+  </si>
+  <si>
+    <t>動的値は、プランディングリソースで定義されている順序で適用されます。動的値が参照されるActivity -Definitionによっても指定されている場合、Activity -Definitionの動的値が最初に適用され、次にここで指定された動的値が続くことに注意してください。さらに、変換値と動的値の両方が固有の場合、動的値は変換の結果に適用されます。 / Dynamic values are applied in the order in which they are defined in the PlanDefinition resource. Note that when dynamic values are also specified by a referenced ActivityDefinition, the dynamicValues from the ActivityDefinition are applied first, followed by the dynamicValues specified here. In addition, if both a transform and dynamic values are specific, the dynamic values are applied to the result of the transform.</t>
   </si>
   <si>
     <t>PlanDefinition.action.dynamicValue.id</t>
@@ -1854,31 +1863,31 @@
     <t>PlanDefinition.action.dynamicValue.path</t>
   </si>
   <si>
-    <t>The path to the element to be set dynamically</t>
-  </si>
-  <si>
-    <t>The path to the element to be customized. This is the path on the resource that will hold the result of the calculation defined by the expression. The specified path SHALL be a FHIRPath resolveable on the specified target type of the ActivityDefinition, and SHALL consist only of identifiers, constant indexers, and a restricted subset of functions. The path is allowed to contain qualifiers (.) to traverse sub-elements, as well as indexers ([x]) to traverse multiple-cardinality sub-elements (see the [Simple FHIRPath Profile](http://hl7.org/fhir/R4B/fhirpath.html#simple) for full details).</t>
-  </si>
-  <si>
-    <t>To specify the path to the current action being realized, the %action environment variable is available in this path. For example, to specify the description element of the target action, the path would be %action.description. The path attribute contains a [Simple FHIRPath Subset](http://hl7.org/fhir/R4B/fhirpath.html#simple) that allows path traversal, but not calculation.</t>
+    <t>動的に設定する要素へのパス / The path to the element to be set dynamically</t>
+  </si>
+  <si>
+    <t>カスタマイズされる要素へのパス。これは、式によって定義された計算の結果を保持するリソースのパスです。指定されたパスは、指定されたターゲットタイプのActivity -Definitionで解決可能なFHIRPATHであり、identifier、一定のインデクサー、および関数の制限付きサブセットのみで構成されます。パスは、サブエレメントを通過する予選（。）を含むことができます。また、インデクサー（[x]）が複数のカードサブエレメントを通過します（[simple fhirpathプロファイル]（fhirpath.html＃simpleを参照）。詳細）。 / The path to the element to be customized. This is the path on the resource that will hold the result of the calculation defined by the expression. The specified path SHALL be a FHIRPath resolveable on the specified target type of the ActivityDefinition, and SHALL consist only of identifiers, constant indexers, and a restricted subset of functions. The path is allowed to contain qualifiers (.) to traverse sub-elements, as well as indexers ([x]) to traverse multiple-cardinality sub-elements (see the [Simple FHIRPath Profile](http://hl7.org/fhir/R4B/fhirpath.html#simple) for full details).</t>
+  </si>
+  <si>
+    <t>実現されている現在のアクションへのパスを指定するために、このパスで％アクション環境変数が利用可能です。たとえば、ターゲットアクションの説明要素を指定するには、パスは％action.descriptionです。パス属性には、[simple fhirpath Subset]（fhirpath.html＃simple）が含まれています。 / To specify the path to the current action being realized, the %action environment variable is available in this path. For example, to specify the description element of the target action, the path would be %action.description. The path attribute contains a [Simple FHIRPath Subset](http://hl7.org/fhir/R4B/fhirpath.html#simple) that allows path traversal, but not calculation.</t>
   </si>
   <si>
     <t>PlanDefinition.action.dynamicValue.expression</t>
   </si>
   <si>
-    <t>An expression that provides the dynamic value for the customization</t>
-  </si>
-  <si>
-    <t>An expression specifying the value of the customized element.</t>
+    <t>カスタマイズの動的値を提供する式 / An expression that provides the dynamic value for the customization</t>
+  </si>
+  <si>
+    <t>カスタマイズされた要素の値を指定する式。 / An expression specifying the value of the customized element.</t>
   </si>
   <si>
     <t>PlanDefinition.action.action</t>
   </si>
   <si>
-    <t>A sub-action</t>
-  </si>
-  <si>
-    <t>Sub actions that are contained within the action. The behavior of this action determines the functionality of the sub-actions. For example, a selection behavior of at-most-one indicates that of the sub-actions, at most one may be chosen as part of realizing the action definition.</t>
+    <t>サブアクション / A sub-action</t>
+  </si>
+  <si>
+    <t>アクション内に含まれるサブアクション。このアクションの動作により、サブアクションの機能が決定されます。たとえば、一時的な1つの選択動作は、サブアクションのうち、せいぜいアクション定義の一部として選択される可能性があることを示しています。 / Sub actions that are contained within the action. The behavior of this action determines the functionality of the sub-actions. For example, a selection behavior of at-most-one indicates that of the sub-actions, at most one may be chosen as part of realizing the action definition.</t>
   </si>
   <si>
     <t>{InverseRelationship of Definition.partOf}</t>
@@ -2212,7 +2221,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="84.578125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="121.94921875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="48.17578125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -9154,7 +9163,7 @@
         <v>78</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>139</v>
+        <v>425</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>78</v>
@@ -9171,10 +9180,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9287,10 +9296,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9316,10 +9325,10 @@
         <v>173</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9370,7 +9379,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9399,10 +9408,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9428,10 +9437,10 @@
         <v>173</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9482,7 +9491,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9511,10 +9520,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9540,10 +9549,10 @@
         <v>173</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9594,7 +9603,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9623,10 +9632,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9652,10 +9661,10 @@
         <v>173</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9706,7 +9715,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9735,10 +9744,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9764,10 +9773,10 @@
         <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9797,10 +9806,10 @@
         <v>206</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>78</v>
@@ -9818,7 +9827,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9836,7 +9845,7 @@
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
@@ -9847,10 +9856,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9876,10 +9885,10 @@
         <v>196</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9909,10 +9918,10 @@
         <v>314</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>78</v>
@@ -9930,7 +9939,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9948,7 +9957,7 @@
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>78</v>
@@ -9959,10 +9968,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9988,13 +9997,13 @@
         <v>196</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10023,10 +10032,10 @@
         <v>314</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>78</v>
@@ -10044,7 +10053,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10062,7 +10071,7 @@
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
@@ -10073,10 +10082,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10102,10 +10111,10 @@
         <v>333</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10156,7 +10165,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10185,10 +10194,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10214,10 +10223,10 @@
         <v>89</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10268,7 +10277,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10297,10 +10306,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10323,19 +10332,19 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10386,7 +10395,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10415,10 +10424,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10441,13 +10450,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10498,7 +10507,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10527,10 +10536,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10556,13 +10565,13 @@
         <v>344</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10612,7 +10621,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10641,10 +10650,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10753,10 +10762,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10867,10 +10876,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10983,10 +10992,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11012,13 +11021,13 @@
         <v>107</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11047,10 +11056,10 @@
         <v>206</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>78</v>
@@ -11068,7 +11077,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>87</v>
@@ -11097,10 +11106,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11123,16 +11132,16 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11182,7 +11191,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11211,10 +11220,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11237,13 +11246,13 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11294,7 +11303,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11323,10 +11332,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11349,13 +11358,13 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11406,7 +11415,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11435,10 +11444,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11464,13 +11473,13 @@
         <v>344</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11520,7 +11529,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11549,10 +11558,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11661,10 +11670,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11775,10 +11784,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11891,10 +11900,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11920,10 +11929,10 @@
         <v>89</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11974,7 +11983,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>87</v>
@@ -12003,10 +12012,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12032,10 +12041,10 @@
         <v>107</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12065,10 +12074,10 @@
         <v>206</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>78</v>
@@ -12086,7 +12095,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>87</v>
@@ -12115,10 +12124,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12141,13 +12150,13 @@
         <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12198,7 +12207,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12227,10 +12236,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12253,16 +12262,16 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12312,7 +12321,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12330,7 +12339,7 @@
         <v>78</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>78</v>
@@ -12341,10 +12350,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12370,10 +12379,10 @@
         <v>344</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12424,7 +12433,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12442,7 +12451,7 @@
         <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
@@ -12453,10 +12462,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12565,10 +12574,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12679,10 +12688,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12795,10 +12804,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12824,10 +12833,10 @@
         <v>107</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12857,10 +12866,10 @@
         <v>206</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>78</v>
@@ -12878,7 +12887,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>87</v>
@@ -12896,7 +12905,7 @@
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>78</v>
@@ -12907,10 +12916,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12936,10 +12945,10 @@
         <v>196</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12969,10 +12978,10 @@
         <v>314</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>78</v>
@@ -12990,7 +12999,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13008,7 +13017,7 @@
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>78</v>
@@ -13019,10 +13028,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13048,10 +13057,10 @@
         <v>196</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13081,10 +13090,10 @@
         <v>199</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>78</v>
@@ -13102,7 +13111,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13120,7 +13129,7 @@
         <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -13131,10 +13140,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13160,10 +13169,10 @@
         <v>107</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13193,10 +13202,10 @@
         <v>206</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>78</v>
@@ -13214,7 +13223,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13243,10 +13252,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13272,10 +13281,10 @@
         <v>107</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13305,10 +13314,10 @@
         <v>206</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>78</v>
@@ -13326,7 +13335,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13355,10 +13364,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13384,10 +13393,10 @@
         <v>107</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13417,10 +13426,10 @@
         <v>206</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>78</v>
@@ -13438,7 +13447,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13467,10 +13476,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13496,10 +13505,10 @@
         <v>107</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13529,10 +13538,10 @@
         <v>206</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>78</v>
@@ -13550,7 +13559,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -13579,10 +13588,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13608,10 +13617,10 @@
         <v>107</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -13641,10 +13650,10 @@
         <v>206</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>78</v>
@@ -13662,7 +13671,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -13691,10 +13700,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13717,16 +13726,16 @@
         <v>78</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13776,7 +13785,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -13791,7 +13800,7 @@
         <v>99</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>416</v>
@@ -13805,10 +13814,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13831,16 +13840,16 @@
         <v>78</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -13890,7 +13899,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -13919,10 +13928,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13948,13 +13957,13 @@
         <v>344</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14004,7 +14013,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14033,10 +14042,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14145,10 +14154,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14259,10 +14268,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14375,10 +14384,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14404,13 +14413,13 @@
         <v>173</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14460,7 +14469,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -14489,10 +14498,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14515,16 +14524,16 @@
         <v>78</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14574,7 +14583,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -14603,10 +14612,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14632,10 +14641,10 @@
         <v>81</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -14686,7 +14695,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -14701,7 +14710,7 @@
         <v>99</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>131</v>
